--- a/AAII_Financials/Yearly/RWEOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RWEOY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
   <si>
     <t>RWEOY</t>
   </si>
@@ -656,197 +656,209 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>41627100</v>
+        <v>31082700</v>
       </c>
       <c r="E8" s="3">
-        <v>26659500</v>
+        <v>41746000</v>
       </c>
       <c r="F8" s="3">
-        <v>14851500</v>
+        <v>26735700</v>
       </c>
       <c r="G8" s="3">
-        <v>14240600</v>
+        <v>14893900</v>
       </c>
       <c r="H8" s="3">
-        <v>14545500</v>
+        <v>14281300</v>
       </c>
       <c r="I8" s="3">
-        <v>14996900</v>
+        <v>14587100</v>
       </c>
       <c r="J8" s="3">
+        <v>15039700</v>
+      </c>
+      <c r="K8" s="3">
         <v>47295200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>48507200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>50344400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>59509800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>55746600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>57696300</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>33908400</v>
+        <v>21745700</v>
       </c>
       <c r="E9" s="3">
-        <v>19194700</v>
+        <v>34005300</v>
       </c>
       <c r="F9" s="3">
-        <v>10546200</v>
+        <v>19249600</v>
       </c>
       <c r="G9" s="3">
-        <v>9744400</v>
+        <v>10576300</v>
       </c>
       <c r="H9" s="3">
-        <v>10799000</v>
+        <v>9772200</v>
       </c>
       <c r="I9" s="3">
-        <v>10814200</v>
+        <v>10829900</v>
       </c>
       <c r="J9" s="3">
+        <v>10845100</v>
+      </c>
+      <c r="K9" s="3">
         <v>35950400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>35441900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>36444000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>42205500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>37643800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>39455300</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>7718700</v>
+        <v>9337000</v>
       </c>
       <c r="E10" s="3">
-        <v>7464800</v>
+        <v>7740700</v>
       </c>
       <c r="F10" s="3">
-        <v>4305300</v>
+        <v>7486100</v>
       </c>
       <c r="G10" s="3">
-        <v>4496200</v>
+        <v>4317600</v>
       </c>
       <c r="H10" s="3">
-        <v>3746500</v>
+        <v>4509100</v>
       </c>
       <c r="I10" s="3">
-        <v>4182700</v>
+        <v>3757200</v>
       </c>
       <c r="J10" s="3">
+        <v>4194600</v>
+      </c>
+      <c r="K10" s="3">
         <v>11344800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>13065200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>13900400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>17304200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>18102700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>18241000</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -863,8 +875,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -904,9 +917,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,93 +962,102 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-2017000</v>
+        <v>1606000</v>
       </c>
       <c r="E14" s="3">
+        <v>-2022800</v>
+      </c>
+      <c r="F14" s="3">
+        <v>595200</v>
+      </c>
+      <c r="G14" s="3">
+        <v>1758400</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1596200</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>424400</v>
+      </c>
+      <c r="K14" s="3">
+        <v>4495200</v>
+      </c>
+      <c r="L14" s="3">
+        <v>2880900</v>
+      </c>
+      <c r="M14" s="3">
         <v>593500</v>
       </c>
-      <c r="F14" s="3">
-        <v>1753400</v>
-      </c>
-      <c r="G14" s="3">
-        <v>1591700</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>423200</v>
-      </c>
-      <c r="J14" s="3">
-        <v>4495200</v>
-      </c>
-      <c r="K14" s="3">
-        <v>2880900</v>
-      </c>
-      <c r="L14" s="3">
-        <v>593500</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>5705900</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1768600</v>
+        <v>2069600</v>
       </c>
       <c r="E15" s="3">
-        <v>1541800</v>
+        <v>1773600</v>
       </c>
       <c r="F15" s="3">
-        <v>1545000</v>
+        <v>1546200</v>
       </c>
       <c r="G15" s="3">
-        <v>1299800</v>
+        <v>1549500</v>
       </c>
       <c r="H15" s="3">
-        <v>977600</v>
+        <v>1303500</v>
       </c>
       <c r="I15" s="3">
-        <v>1032900</v>
+        <v>980400</v>
       </c>
       <c r="J15" s="3">
+        <v>1035900</v>
+      </c>
+      <c r="K15" s="3">
         <v>2459700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2551900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2478500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2997700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>5568000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3995600</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1046,92 +1071,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>42037200</v>
+        <v>26820600</v>
       </c>
       <c r="E17" s="3">
-        <v>25450800</v>
+        <v>42157300</v>
       </c>
       <c r="F17" s="3">
-        <v>13332500</v>
+        <v>25523600</v>
       </c>
       <c r="G17" s="3">
-        <v>14395800</v>
+        <v>13370600</v>
       </c>
       <c r="H17" s="3">
-        <v>14231900</v>
+        <v>14436900</v>
       </c>
       <c r="I17" s="3">
-        <v>12868100</v>
+        <v>14272600</v>
       </c>
       <c r="J17" s="3">
+        <v>12904900</v>
+      </c>
+      <c r="K17" s="3">
         <v>51764300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>48012000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>46471700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>59888900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>51524700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>52849600</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-410100</v>
+        <v>4262100</v>
       </c>
       <c r="E18" s="3">
-        <v>1208700</v>
+        <v>-411300</v>
       </c>
       <c r="F18" s="3">
-        <v>1519000</v>
+        <v>1212100</v>
       </c>
       <c r="G18" s="3">
-        <v>-155200</v>
+        <v>1523300</v>
       </c>
       <c r="H18" s="3">
-        <v>313600</v>
+        <v>-155600</v>
       </c>
       <c r="I18" s="3">
-        <v>2128800</v>
+        <v>314500</v>
       </c>
       <c r="J18" s="3">
+        <v>2134900</v>
+      </c>
+      <c r="K18" s="3">
         <v>-4469100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>495100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3872700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-379200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4221800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4846700</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1148,218 +1180,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>2071300</v>
+        <v>1196900</v>
       </c>
       <c r="E20" s="3">
-        <v>811600</v>
+        <v>2077200</v>
       </c>
       <c r="F20" s="3">
-        <v>174700</v>
+        <v>813900</v>
       </c>
       <c r="G20" s="3">
-        <v>-380800</v>
+        <v>175200</v>
       </c>
       <c r="H20" s="3">
-        <v>-65100</v>
+        <v>-381900</v>
       </c>
       <c r="I20" s="3">
-        <v>425300</v>
+        <v>-65300</v>
       </c>
       <c r="J20" s="3">
+        <v>426500</v>
+      </c>
+      <c r="K20" s="3">
         <v>-839800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-38100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-244400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>570600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-401900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-49300</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E21" s="3">
-        <v>4316400</v>
+      <c r="E21" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F21" s="3">
-        <v>5141600</v>
+        <v>4343300</v>
       </c>
       <c r="G21" s="3">
-        <v>2451000</v>
+        <v>5178200</v>
       </c>
       <c r="H21" s="3">
-        <v>1287500</v>
+        <v>2477000</v>
       </c>
       <c r="I21" s="3">
-        <v>3604000</v>
+        <v>1297800</v>
       </c>
       <c r="J21" s="3">
+        <v>3621000</v>
+      </c>
+      <c r="K21" s="3">
         <v>1925400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>6391200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7042800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8901000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>9709900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8841500</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>885400</v>
+        <v>1100100</v>
       </c>
       <c r="E22" s="3">
-        <v>368900</v>
+        <v>887900</v>
       </c>
       <c r="F22" s="3">
-        <v>321200</v>
+        <v>370000</v>
       </c>
       <c r="G22" s="3">
-        <v>279900</v>
+        <v>322100</v>
       </c>
       <c r="H22" s="3">
-        <v>195300</v>
+        <v>280700</v>
       </c>
       <c r="I22" s="3">
-        <v>323300</v>
+        <v>195900</v>
       </c>
       <c r="J22" s="3">
+        <v>324300</v>
+      </c>
+      <c r="K22" s="3">
         <v>991700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1131000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1178200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2602900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1371400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1247800</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>775800</v>
+        <v>4358900</v>
       </c>
       <c r="E23" s="3">
-        <v>1651400</v>
+        <v>778000</v>
       </c>
       <c r="F23" s="3">
-        <v>1372500</v>
+        <v>1656100</v>
       </c>
       <c r="G23" s="3">
-        <v>-815900</v>
+        <v>1376400</v>
       </c>
       <c r="H23" s="3">
-        <v>53200</v>
+        <v>-818300</v>
       </c>
       <c r="I23" s="3">
-        <v>2230800</v>
+        <v>53300</v>
       </c>
       <c r="J23" s="3">
+        <v>2237100</v>
+      </c>
+      <c r="K23" s="3">
         <v>-6300600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-673900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2450200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2411500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2448500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3549600</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-2470500</v>
+        <v>2621200</v>
       </c>
       <c r="E24" s="3">
-        <v>748700</v>
+        <v>-2477600</v>
       </c>
       <c r="F24" s="3">
-        <v>408000</v>
+        <v>750800</v>
       </c>
       <c r="G24" s="3">
-        <v>-99800</v>
+        <v>409100</v>
       </c>
       <c r="H24" s="3">
-        <v>111800</v>
+        <v>-100100</v>
       </c>
       <c r="I24" s="3">
-        <v>361300</v>
+        <v>112100</v>
       </c>
       <c r="J24" s="3">
+        <v>362300</v>
+      </c>
+      <c r="K24" s="3">
         <v>-350500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>638000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>603300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>884000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>577500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1002400</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1399,93 +1447,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>3246300</v>
+        <v>1737700</v>
       </c>
       <c r="E26" s="3">
-        <v>902700</v>
+        <v>3255600</v>
       </c>
       <c r="F26" s="3">
-        <v>964600</v>
+        <v>905300</v>
       </c>
       <c r="G26" s="3">
-        <v>-716100</v>
+        <v>967300</v>
       </c>
       <c r="H26" s="3">
-        <v>-58600</v>
+        <v>-718100</v>
       </c>
       <c r="I26" s="3">
-        <v>1869500</v>
+        <v>-58800</v>
       </c>
       <c r="J26" s="3">
+        <v>1874800</v>
+      </c>
+      <c r="K26" s="3">
         <v>-5950100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-1311900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1846900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-3295500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1871000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2547200</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>2947900</v>
+        <v>1577700</v>
       </c>
       <c r="E27" s="3">
-        <v>782300</v>
+        <v>2956400</v>
       </c>
       <c r="F27" s="3">
-        <v>900600</v>
+        <v>784500</v>
       </c>
       <c r="G27" s="3">
-        <v>-1430000</v>
+        <v>903100</v>
       </c>
       <c r="H27" s="3">
-        <v>-859300</v>
+        <v>-1434100</v>
       </c>
       <c r="I27" s="3">
-        <v>1419200</v>
+        <v>-861800</v>
       </c>
       <c r="J27" s="3">
+        <v>1423200</v>
+      </c>
+      <c r="K27" s="3">
         <v>-6195400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-1792300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1461800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-3671100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1434000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2119900</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1525,9 +1582,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1537,39 +1597,42 @@
       <c r="E29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="3">
-        <v>239800</v>
+      <c r="F29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G29" s="3">
-        <v>10650400</v>
+        <v>240500</v>
       </c>
       <c r="H29" s="3">
-        <v>1222800</v>
+        <v>10680800</v>
       </c>
       <c r="I29" s="3">
-        <v>642300</v>
-      </c>
-      <c r="J29" s="3" t="s">
+        <v>1226300</v>
+      </c>
+      <c r="J29" s="3">
+        <v>644200</v>
+      </c>
+      <c r="K29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>1612400</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>397100</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>373200</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1609,9 +1672,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1651,93 +1717,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2071300</v>
+        <v>-1196900</v>
       </c>
       <c r="E32" s="3">
-        <v>-811600</v>
+        <v>-2077200</v>
       </c>
       <c r="F32" s="3">
-        <v>-174700</v>
+        <v>-813900</v>
       </c>
       <c r="G32" s="3">
-        <v>380800</v>
+        <v>-175200</v>
       </c>
       <c r="H32" s="3">
-        <v>65100</v>
+        <v>381900</v>
       </c>
       <c r="I32" s="3">
-        <v>-425300</v>
+        <v>65300</v>
       </c>
       <c r="J32" s="3">
+        <v>-426500</v>
+      </c>
+      <c r="K32" s="3">
         <v>839800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>38100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>244400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-570600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>401900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>49300</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2947900</v>
+        <v>1577700</v>
       </c>
       <c r="E33" s="3">
-        <v>782300</v>
+        <v>2956400</v>
       </c>
       <c r="F33" s="3">
-        <v>1140300</v>
+        <v>784500</v>
       </c>
       <c r="G33" s="3">
-        <v>9220300</v>
+        <v>1143600</v>
       </c>
       <c r="H33" s="3">
-        <v>363500</v>
+        <v>9246700</v>
       </c>
       <c r="I33" s="3">
-        <v>2061500</v>
+        <v>364500</v>
       </c>
       <c r="J33" s="3">
+        <v>2067400</v>
+      </c>
+      <c r="K33" s="3">
         <v>-6195400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-179900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1858900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-3297900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1434000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2119900</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1777,98 +1852,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2947900</v>
+        <v>1577700</v>
       </c>
       <c r="E35" s="3">
-        <v>782300</v>
+        <v>2956400</v>
       </c>
       <c r="F35" s="3">
-        <v>1140300</v>
+        <v>784500</v>
       </c>
       <c r="G35" s="3">
-        <v>9220300</v>
+        <v>1143600</v>
       </c>
       <c r="H35" s="3">
-        <v>363500</v>
+        <v>9246700</v>
       </c>
       <c r="I35" s="3">
-        <v>2061500</v>
+        <v>364500</v>
       </c>
       <c r="J35" s="3">
+        <v>2067400</v>
+      </c>
+      <c r="K35" s="3">
         <v>-6195400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-179900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1858900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-3297900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1434000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2119900</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1885,8 +1969,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1903,386 +1988,414 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>7582000</v>
+        <v>7526400</v>
       </c>
       <c r="E41" s="3">
-        <v>6320100</v>
+        <v>7603600</v>
       </c>
       <c r="F41" s="3">
-        <v>5179800</v>
+        <v>6338200</v>
       </c>
       <c r="G41" s="3">
-        <v>6926600</v>
+        <v>5194600</v>
       </c>
       <c r="H41" s="3">
-        <v>3822500</v>
+        <v>6946400</v>
       </c>
       <c r="I41" s="3">
-        <v>4267300</v>
+        <v>3833400</v>
       </c>
       <c r="J41" s="3">
+        <v>4279500</v>
+      </c>
+      <c r="K41" s="3">
         <v>4965000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2668300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3459300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>9450000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5662400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>4307900</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>14612800</v>
+        <v>8404500</v>
       </c>
       <c r="E42" s="3">
-        <v>8723400</v>
+        <v>14654500</v>
       </c>
       <c r="F42" s="3">
-        <v>4577600</v>
+        <v>8748300</v>
       </c>
       <c r="G42" s="3">
-        <v>3534900</v>
+        <v>4590700</v>
       </c>
       <c r="H42" s="3">
-        <v>3915800</v>
+        <v>3545000</v>
       </c>
       <c r="I42" s="3">
-        <v>5308900</v>
+        <v>3927000</v>
       </c>
       <c r="J42" s="3">
+        <v>5324100</v>
+      </c>
+      <c r="K42" s="3">
         <v>10660100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>7868300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4810900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>3364900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>6012600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>12134800</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>20262400</v>
+        <v>11565400</v>
       </c>
       <c r="E43" s="3">
-        <v>20930700</v>
+        <v>20320300</v>
       </c>
       <c r="F43" s="3">
-        <v>9465500</v>
+        <v>20990500</v>
       </c>
       <c r="G43" s="3">
-        <v>10629700</v>
+        <v>9492600</v>
       </c>
       <c r="H43" s="3">
-        <v>5257900</v>
+        <v>10660100</v>
       </c>
       <c r="I43" s="3">
-        <v>8240600</v>
+        <v>5272900</v>
       </c>
       <c r="J43" s="3">
+        <v>8264100</v>
+      </c>
+      <c r="K43" s="3">
         <v>7273800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7230400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>9334900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>20488500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>32414100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>24880100</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>4563500</v>
+        <v>2470000</v>
       </c>
       <c r="E44" s="3">
-        <v>3068400</v>
+        <v>4576500</v>
       </c>
       <c r="F44" s="3">
-        <v>3541400</v>
+        <v>3077100</v>
       </c>
       <c r="G44" s="3">
-        <v>3439400</v>
+        <v>3551600</v>
       </c>
       <c r="H44" s="3">
-        <v>1769600</v>
+        <v>3449300</v>
       </c>
       <c r="I44" s="3">
-        <v>2087500</v>
+        <v>1774700</v>
       </c>
       <c r="J44" s="3">
+        <v>2093500</v>
+      </c>
+      <c r="K44" s="3">
         <v>2135300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2072600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2434900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5710700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>10333300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>7845700</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>57423600</v>
+        <v>28782400</v>
       </c>
       <c r="E45" s="3">
-        <v>73196300</v>
+        <v>57587700</v>
       </c>
       <c r="F45" s="3">
-        <v>25403100</v>
+        <v>73405400</v>
       </c>
       <c r="G45" s="3">
-        <v>31835000</v>
+        <v>25475700</v>
       </c>
       <c r="H45" s="3">
-        <v>51975800</v>
+        <v>31925900</v>
       </c>
       <c r="I45" s="3">
-        <v>5446700</v>
+        <v>52124300</v>
       </c>
       <c r="J45" s="3">
+        <v>5462300</v>
+      </c>
+      <c r="K45" s="3">
         <v>8048500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>9658500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>14969500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>16431000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>19849600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>19187100</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>104444000</v>
+        <v>58748700</v>
       </c>
       <c r="E46" s="3">
-        <v>112239000</v>
+        <v>104743000</v>
       </c>
       <c r="F46" s="3">
-        <v>29538000</v>
+        <v>112560000</v>
       </c>
       <c r="G46" s="3">
-        <v>30641500</v>
+        <v>29622400</v>
       </c>
       <c r="H46" s="3">
-        <v>66741600</v>
+        <v>30729000</v>
       </c>
       <c r="I46" s="3">
-        <v>25351000</v>
+        <v>66932300</v>
       </c>
       <c r="J46" s="3">
+        <v>25423500</v>
+      </c>
+      <c r="K46" s="3">
         <v>33082700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>29498100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>35009500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>29278200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>27423600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>34177800</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>9136800</v>
+        <v>10965900</v>
       </c>
       <c r="E47" s="3">
-        <v>9593600</v>
+        <v>9162900</v>
       </c>
       <c r="F47" s="3">
-        <v>8447800</v>
+        <v>9621000</v>
       </c>
       <c r="G47" s="3">
-        <v>8690900</v>
+        <v>8471900</v>
       </c>
       <c r="H47" s="3">
-        <v>2412000</v>
+        <v>8715700</v>
       </c>
       <c r="I47" s="3">
-        <v>4936800</v>
+        <v>2418800</v>
       </c>
       <c r="J47" s="3">
+        <v>4950900</v>
+      </c>
+      <c r="K47" s="3">
         <v>4974700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4795900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5536400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6894900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>13053000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>16227900</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>25767700</v>
+        <v>31347100</v>
       </c>
       <c r="E48" s="3">
-        <v>21682600</v>
+        <v>25841300</v>
       </c>
       <c r="F48" s="3">
-        <v>38848400</v>
+        <v>21744600</v>
       </c>
       <c r="G48" s="3">
-        <v>41208300</v>
+        <v>38959400</v>
       </c>
       <c r="H48" s="3">
-        <v>13463800</v>
+        <v>41326000</v>
       </c>
       <c r="I48" s="3">
-        <v>27067500</v>
+        <v>13502200</v>
       </c>
       <c r="J48" s="3">
+        <v>27144800</v>
+      </c>
+      <c r="K48" s="3">
         <v>26602000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>31135900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>33973100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>89657600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>120179000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>82126800</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>6131300</v>
+        <v>10624200</v>
       </c>
       <c r="E49" s="3">
-        <v>6353800</v>
+        <v>6148900</v>
       </c>
       <c r="F49" s="3">
-        <v>10635200</v>
+        <v>6371900</v>
       </c>
       <c r="G49" s="3">
-        <v>10451800</v>
+        <v>10665600</v>
       </c>
       <c r="H49" s="3">
-        <v>2369600</v>
+        <v>10481700</v>
       </c>
       <c r="I49" s="3">
-        <v>13401900</v>
+        <v>2376400</v>
       </c>
       <c r="J49" s="3">
+        <v>13440200</v>
+      </c>
+      <c r="K49" s="3">
         <v>13826200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>13975100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>13959300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>45685300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>53012500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>39782800</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2322,9 +2435,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2364,51 +2480,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4844500</v>
+        <v>4190300</v>
       </c>
       <c r="E52" s="3">
-        <v>4536400</v>
+        <v>4858400</v>
       </c>
       <c r="F52" s="3">
-        <v>8189600</v>
+        <v>4549300</v>
       </c>
       <c r="G52" s="3">
-        <v>8289400</v>
+        <v>8213000</v>
       </c>
       <c r="H52" s="3">
-        <v>1930200</v>
+        <v>8313100</v>
       </c>
       <c r="I52" s="3">
-        <v>4171800</v>
+        <v>1935700</v>
       </c>
       <c r="J52" s="3">
+        <v>4183700</v>
+      </c>
+      <c r="K52" s="3">
         <v>4410500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4530400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5684700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7292000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>12964100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10999800</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2448,51 +2570,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>150325000</v>
+        <v>115876000</v>
       </c>
       <c r="E54" s="3">
-        <v>154405000</v>
+        <v>150754000</v>
       </c>
       <c r="F54" s="3">
-        <v>66881600</v>
+        <v>154846000</v>
       </c>
       <c r="G54" s="3">
-        <v>69449800</v>
+        <v>67072700</v>
       </c>
       <c r="H54" s="3">
-        <v>86917200</v>
+        <v>69648200</v>
       </c>
       <c r="I54" s="3">
-        <v>74929000</v>
+        <v>87165500</v>
       </c>
       <c r="J54" s="3">
+        <v>75143100</v>
+      </c>
+      <c r="K54" s="3">
         <v>82896200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>83935400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>94163000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>97348000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>97097200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>108732000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2509,8 +2637,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2527,260 +2656,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>8098400</v>
+        <v>5564500</v>
       </c>
       <c r="E57" s="3">
-        <v>4804400</v>
+        <v>8121600</v>
       </c>
       <c r="F57" s="3">
-        <v>2589900</v>
+        <v>4818100</v>
       </c>
       <c r="G57" s="3">
-        <v>3240900</v>
+        <v>2597300</v>
       </c>
       <c r="H57" s="3">
-        <v>2635500</v>
+        <v>3250200</v>
       </c>
       <c r="I57" s="3">
-        <v>5508500</v>
+        <v>2643000</v>
       </c>
       <c r="J57" s="3">
+        <v>5524300</v>
+      </c>
+      <c r="K57" s="3">
         <v>5892600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6477100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6882600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7703500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>16086800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>18513300</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>9413500</v>
+        <v>1192600</v>
       </c>
       <c r="E58" s="3">
-        <v>6906000</v>
+        <v>9440400</v>
       </c>
       <c r="F58" s="3">
-        <v>1536400</v>
+        <v>6925800</v>
       </c>
       <c r="G58" s="3">
-        <v>2346900</v>
+        <v>1540700</v>
       </c>
       <c r="H58" s="3">
-        <v>98700</v>
+        <v>2353600</v>
       </c>
       <c r="I58" s="3">
-        <v>1864000</v>
+        <v>99000</v>
       </c>
       <c r="J58" s="3">
+        <v>1869400</v>
+      </c>
+      <c r="K58" s="3">
         <v>958100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1298200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2391300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3765600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>12557800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>15247800</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>68946300</v>
+        <v>30531000</v>
       </c>
       <c r="E59" s="3">
-        <v>93542200</v>
+        <v>69143300</v>
       </c>
       <c r="F59" s="3">
-        <v>25201300</v>
+        <v>93809500</v>
       </c>
       <c r="G59" s="3">
-        <v>31839300</v>
+        <v>25273300</v>
       </c>
       <c r="H59" s="3">
-        <v>47006500</v>
+        <v>31930300</v>
       </c>
       <c r="I59" s="3">
-        <v>14646400</v>
+        <v>47140800</v>
       </c>
       <c r="J59" s="3">
+        <v>14688300</v>
+      </c>
+      <c r="K59" s="3">
         <v>24360400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>18807000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>21511700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>34417100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>42894500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>39444700</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>86458200</v>
+        <v>37288100</v>
       </c>
       <c r="E60" s="3">
-        <v>105253000</v>
+        <v>86705200</v>
       </c>
       <c r="F60" s="3">
-        <v>17903600</v>
+        <v>105553000</v>
       </c>
       <c r="G60" s="3">
-        <v>21271400</v>
+        <v>17954700</v>
       </c>
       <c r="H60" s="3">
-        <v>49740700</v>
+        <v>21332200</v>
       </c>
       <c r="I60" s="3">
-        <v>22019000</v>
+        <v>49882900</v>
       </c>
       <c r="J60" s="3">
+        <v>22081900</v>
+      </c>
+      <c r="K60" s="3">
         <v>31211100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>26582300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>30785500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26150100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>26651800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>36602900</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>9259400</v>
+        <v>13680700</v>
       </c>
       <c r="E61" s="3">
-        <v>6248500</v>
+        <v>9285800</v>
       </c>
       <c r="F61" s="3">
-        <v>3577200</v>
+        <v>6266400</v>
       </c>
       <c r="G61" s="3">
-        <v>3366800</v>
+        <v>3587500</v>
       </c>
       <c r="H61" s="3">
-        <v>1960600</v>
+        <v>3376400</v>
       </c>
       <c r="I61" s="3">
-        <v>14787500</v>
+        <v>1966200</v>
       </c>
       <c r="J61" s="3">
+        <v>14829700</v>
+      </c>
+      <c r="K61" s="3">
         <v>16589600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>16969300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>15528000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>18527900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>16927900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>18109500</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>22839300</v>
+        <v>28847700</v>
       </c>
       <c r="E62" s="3">
-        <v>24463500</v>
+        <v>22904500</v>
       </c>
       <c r="F62" s="3">
-        <v>49649600</v>
+        <v>24533400</v>
       </c>
       <c r="G62" s="3">
-        <v>50487200</v>
+        <v>49791500</v>
       </c>
       <c r="H62" s="3">
-        <v>19747000</v>
+        <v>50631500</v>
       </c>
       <c r="I62" s="3">
-        <v>25112300</v>
+        <v>19803400</v>
       </c>
       <c r="J62" s="3">
+        <v>25184100</v>
+      </c>
+      <c r="K62" s="3">
         <v>26426300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>30974000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>35007300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>73540000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>104377000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>67904900</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2820,9 +2968,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2862,9 +3013,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2904,51 +3058,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>120405000</v>
+        <v>81525900</v>
       </c>
       <c r="E66" s="3">
-        <v>137855000</v>
+        <v>120749000</v>
       </c>
       <c r="F66" s="3">
-        <v>48527700</v>
+        <v>138249000</v>
       </c>
       <c r="G66" s="3">
-        <v>51043800</v>
+        <v>48666400</v>
       </c>
       <c r="H66" s="3">
-        <v>77438600</v>
+        <v>51189700</v>
       </c>
       <c r="I66" s="3">
-        <v>67595500</v>
+        <v>77659900</v>
       </c>
       <c r="J66" s="3">
+        <v>67788600</v>
+      </c>
+      <c r="K66" s="3">
         <v>79908100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>77749200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>86103300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>88091800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>83733500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>92266200</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2965,8 +3125,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3006,9 +3167,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3048,9 +3212,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3085,14 +3252,17 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3">
         <v>109800</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>117400</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3132,51 +3302,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>17070300</v>
+        <v>15682800</v>
       </c>
       <c r="E72" s="3">
-        <v>11614900</v>
+        <v>17119100</v>
       </c>
       <c r="F72" s="3">
-        <v>9008800</v>
+        <v>11648100</v>
       </c>
       <c r="G72" s="3">
-        <v>9665200</v>
+        <v>9034500</v>
       </c>
       <c r="H72" s="3">
-        <v>1235800</v>
+        <v>9692800</v>
       </c>
       <c r="I72" s="3">
-        <v>2568200</v>
+        <v>1239300</v>
       </c>
       <c r="J72" s="3">
+        <v>2575500</v>
+      </c>
+      <c r="K72" s="3">
         <v>-707400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3821500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5463300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>8908100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>24317400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>15423900</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3216,9 +3392,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3258,9 +3437,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3300,51 +3482,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>29920000</v>
+        <v>34350200</v>
       </c>
       <c r="E76" s="3">
-        <v>16550600</v>
+        <v>30005400</v>
       </c>
       <c r="F76" s="3">
-        <v>18353900</v>
+        <v>16597900</v>
       </c>
       <c r="G76" s="3">
-        <v>18405900</v>
+        <v>18406300</v>
       </c>
       <c r="H76" s="3">
-        <v>9478600</v>
+        <v>18458500</v>
       </c>
       <c r="I76" s="3">
-        <v>7333500</v>
+        <v>9505600</v>
       </c>
       <c r="J76" s="3">
+        <v>7354500</v>
+      </c>
+      <c r="K76" s="3">
         <v>2988100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6186100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8059600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9256200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13254000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>16348800</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3384,98 +3572,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2947900</v>
+        <v>1577700</v>
       </c>
       <c r="E81" s="3">
-        <v>782300</v>
+        <v>2956400</v>
       </c>
       <c r="F81" s="3">
-        <v>1140300</v>
+        <v>784500</v>
       </c>
       <c r="G81" s="3">
-        <v>9220300</v>
+        <v>1143600</v>
       </c>
       <c r="H81" s="3">
-        <v>363500</v>
+        <v>9246700</v>
       </c>
       <c r="I81" s="3">
-        <v>2061500</v>
+        <v>364500</v>
       </c>
       <c r="J81" s="3">
+        <v>2067400</v>
+      </c>
+      <c r="K81" s="3">
         <v>-6195400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-179900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1858900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-3297900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1434000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2119900</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3492,50 +3689,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="D83" s="3">
+        <v>4157600</v>
+      </c>
+      <c r="E83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E83" s="3">
-        <v>2296900</v>
-      </c>
       <c r="F83" s="3">
-        <v>3449200</v>
+        <v>2303500</v>
       </c>
       <c r="G83" s="3">
-        <v>2988100</v>
+        <v>3459100</v>
       </c>
       <c r="H83" s="3">
-        <v>1039400</v>
+        <v>2996600</v>
       </c>
       <c r="I83" s="3">
-        <v>1050300</v>
+        <v>1042400</v>
       </c>
       <c r="J83" s="3">
+        <v>1053300</v>
+      </c>
+      <c r="K83" s="3">
         <v>7237000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>5954400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3363300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>8745400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>5880900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4041400</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3575,9 +3776,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3617,9 +3821,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3659,9 +3866,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3701,9 +3911,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3743,51 +3956,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>2610500</v>
+        <v>4608100</v>
       </c>
       <c r="E89" s="3">
-        <v>7892300</v>
+        <v>2618000</v>
       </c>
       <c r="F89" s="3">
-        <v>4529900</v>
+        <v>7914800</v>
       </c>
       <c r="G89" s="3">
-        <v>-1652500</v>
+        <v>4542800</v>
       </c>
       <c r="H89" s="3">
-        <v>7213100</v>
+        <v>-1657200</v>
       </c>
       <c r="I89" s="3">
-        <v>-1903100</v>
+        <v>7233700</v>
       </c>
       <c r="J89" s="3">
+        <v>-1908500</v>
+      </c>
+      <c r="K89" s="3">
         <v>2551900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3400400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6946900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6670000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4825700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6467700</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3804,50 +4023,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-4865100</v>
+        <v>-10858100</v>
       </c>
       <c r="E91" s="3">
-        <v>-4089400</v>
+        <v>-4879000</v>
       </c>
       <c r="F91" s="3">
-        <v>-3643400</v>
+        <v>-4101000</v>
       </c>
       <c r="G91" s="3">
-        <v>-1921500</v>
+        <v>-3653800</v>
       </c>
       <c r="H91" s="3">
-        <v>-1351900</v>
+        <v>-1927000</v>
       </c>
       <c r="I91" s="3">
-        <v>-3403600</v>
+        <v>-1355800</v>
       </c>
       <c r="J91" s="3">
+        <v>-3413400</v>
+      </c>
+      <c r="K91" s="3">
         <v>-2504200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3357000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3654500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4696300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5578900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-7457200</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3887,9 +4110,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3929,51 +4155,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-10732800</v>
+        <v>-3057600</v>
       </c>
       <c r="E94" s="3">
-        <v>-8395700</v>
+        <v>-10763500</v>
       </c>
       <c r="F94" s="3">
-        <v>-4724100</v>
+        <v>-8419700</v>
       </c>
       <c r="G94" s="3">
-        <v>-791000</v>
+        <v>-4737600</v>
       </c>
       <c r="H94" s="3">
-        <v>-4778300</v>
+        <v>-793200</v>
       </c>
       <c r="I94" s="3">
-        <v>2919700</v>
+        <v>-4792000</v>
       </c>
       <c r="J94" s="3">
+        <v>2928100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-4958500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2016500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5311600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2796700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1410900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9115800</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3990,50 +4222,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-990600</v>
+        <v>-1026100</v>
       </c>
       <c r="E96" s="3">
-        <v>-792100</v>
+        <v>-993400</v>
       </c>
       <c r="F96" s="3">
-        <v>-566400</v>
+        <v>-794300</v>
       </c>
       <c r="G96" s="3">
-        <v>-607600</v>
+        <v>-568000</v>
       </c>
       <c r="H96" s="3">
-        <v>-1112100</v>
+        <v>-609300</v>
       </c>
       <c r="I96" s="3">
-        <v>-172500</v>
+        <v>-1115300</v>
       </c>
       <c r="J96" s="3">
+        <v>-173000</v>
+      </c>
+      <c r="K96" s="3">
         <v>-441600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1132100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1157500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1927100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1708500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2700900</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4073,9 +4309,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4115,9 +4354,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4157,133 +4399,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>9347300</v>
+        <v>-1694200</v>
       </c>
       <c r="E100" s="3">
-        <v>1580800</v>
+        <v>9374000</v>
       </c>
       <c r="F100" s="3">
-        <v>1925900</v>
+        <v>1585400</v>
       </c>
       <c r="G100" s="3">
-        <v>243000</v>
+        <v>1931400</v>
       </c>
       <c r="H100" s="3">
-        <v>-1074200</v>
+        <v>243700</v>
       </c>
       <c r="I100" s="3">
-        <v>-1666600</v>
+        <v>-1077200</v>
       </c>
       <c r="J100" s="3">
+        <v>-1671300</v>
+      </c>
+      <c r="K100" s="3">
         <v>4646000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2161500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2400000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2385200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2704400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2044800</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>36900</v>
+        <v>66400</v>
       </c>
       <c r="E101" s="3">
-        <v>62900</v>
+        <v>37000</v>
       </c>
       <c r="F101" s="3">
-        <v>-36900</v>
+        <v>63100</v>
       </c>
       <c r="G101" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="H101" s="3">
         <v>16300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>14100</v>
       </c>
-      <c r="I101" s="3">
-        <v>-20600</v>
-      </c>
       <c r="J101" s="3">
+        <v>-20700</v>
+      </c>
+      <c r="K101" s="3">
         <v>-26000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>14800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>8700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-21500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>17600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-14100</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1261900</v>
+        <v>-77300</v>
       </c>
       <c r="E102" s="3">
-        <v>1140300</v>
+        <v>1265500</v>
       </c>
       <c r="F102" s="3">
-        <v>1694800</v>
+        <v>1143600</v>
       </c>
       <c r="G102" s="3">
-        <v>-2184100</v>
+        <v>1699600</v>
       </c>
       <c r="H102" s="3">
-        <v>1374700</v>
+        <v>-2190300</v>
       </c>
       <c r="I102" s="3">
-        <v>-670500</v>
+        <v>1378600</v>
       </c>
       <c r="J102" s="3">
+        <v>-672400</v>
+      </c>
+      <c r="K102" s="3">
         <v>2213400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-762800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-756000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1466500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>728000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-617400</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/RWEOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RWEOY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
   <si>
     <t>RWEOY</t>
   </si>
@@ -728,25 +728,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>31082700</v>
+        <v>30871300</v>
       </c>
       <c r="E8" s="3">
-        <v>41746000</v>
+        <v>41462100</v>
       </c>
       <c r="F8" s="3">
-        <v>26735700</v>
+        <v>26553900</v>
       </c>
       <c r="G8" s="3">
-        <v>14893900</v>
+        <v>14792600</v>
       </c>
       <c r="H8" s="3">
-        <v>14281300</v>
+        <v>14184200</v>
       </c>
       <c r="I8" s="3">
-        <v>14587100</v>
+        <v>14487900</v>
       </c>
       <c r="J8" s="3">
-        <v>15039700</v>
+        <v>14937400</v>
       </c>
       <c r="K8" s="3">
         <v>47295200</v>
@@ -773,25 +773,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>21745700</v>
+        <v>21597800</v>
       </c>
       <c r="E9" s="3">
-        <v>34005300</v>
+        <v>33774000</v>
       </c>
       <c r="F9" s="3">
-        <v>19249600</v>
+        <v>19118700</v>
       </c>
       <c r="G9" s="3">
-        <v>10576300</v>
+        <v>10504400</v>
       </c>
       <c r="H9" s="3">
-        <v>9772200</v>
+        <v>9705800</v>
       </c>
       <c r="I9" s="3">
-        <v>10829900</v>
+        <v>10756200</v>
       </c>
       <c r="J9" s="3">
-        <v>10845100</v>
+        <v>10771300</v>
       </c>
       <c r="K9" s="3">
         <v>35950400</v>
@@ -818,25 +818,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>9337000</v>
+        <v>9273500</v>
       </c>
       <c r="E10" s="3">
-        <v>7740700</v>
+        <v>7688100</v>
       </c>
       <c r="F10" s="3">
-        <v>7486100</v>
+        <v>7435200</v>
       </c>
       <c r="G10" s="3">
-        <v>4317600</v>
+        <v>4288200</v>
       </c>
       <c r="H10" s="3">
-        <v>4509100</v>
+        <v>4478400</v>
       </c>
       <c r="I10" s="3">
-        <v>3757200</v>
+        <v>3731700</v>
       </c>
       <c r="J10" s="3">
-        <v>4194600</v>
+        <v>4166100</v>
       </c>
       <c r="K10" s="3">
         <v>11344800</v>
@@ -972,25 +972,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1606000</v>
+        <v>1595100</v>
       </c>
       <c r="E14" s="3">
-        <v>-2022800</v>
+        <v>-2009000</v>
       </c>
       <c r="F14" s="3">
-        <v>595200</v>
+        <v>591100</v>
       </c>
       <c r="G14" s="3">
-        <v>1758400</v>
+        <v>1746400</v>
       </c>
       <c r="H14" s="3">
-        <v>1596200</v>
+        <v>1585400</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
       <c r="J14" s="3">
-        <v>424400</v>
+        <v>421500</v>
       </c>
       <c r="K14" s="3">
         <v>4495200</v>
@@ -1017,25 +1017,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2069600</v>
+        <v>2055500</v>
       </c>
       <c r="E15" s="3">
-        <v>1773600</v>
+        <v>1761500</v>
       </c>
       <c r="F15" s="3">
-        <v>1546200</v>
+        <v>1535700</v>
       </c>
       <c r="G15" s="3">
-        <v>1549500</v>
+        <v>1538900</v>
       </c>
       <c r="H15" s="3">
-        <v>1303500</v>
+        <v>1294700</v>
       </c>
       <c r="I15" s="3">
-        <v>980400</v>
+        <v>973700</v>
       </c>
       <c r="J15" s="3">
-        <v>1035900</v>
+        <v>1028800</v>
       </c>
       <c r="K15" s="3">
         <v>2459700</v>
@@ -1078,25 +1078,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>26820600</v>
+        <v>26638200</v>
       </c>
       <c r="E17" s="3">
-        <v>42157300</v>
+        <v>41870600</v>
       </c>
       <c r="F17" s="3">
-        <v>25523600</v>
+        <v>25350000</v>
       </c>
       <c r="G17" s="3">
-        <v>13370600</v>
+        <v>13279600</v>
       </c>
       <c r="H17" s="3">
-        <v>14436900</v>
+        <v>14338700</v>
       </c>
       <c r="I17" s="3">
-        <v>14272600</v>
+        <v>14175500</v>
       </c>
       <c r="J17" s="3">
-        <v>12904900</v>
+        <v>12817100</v>
       </c>
       <c r="K17" s="3">
         <v>51764300</v>
@@ -1123,25 +1123,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4262100</v>
+        <v>4233100</v>
       </c>
       <c r="E18" s="3">
-        <v>-411300</v>
+        <v>-408500</v>
       </c>
       <c r="F18" s="3">
-        <v>1212100</v>
+        <v>1203900</v>
       </c>
       <c r="G18" s="3">
-        <v>1523300</v>
+        <v>1513000</v>
       </c>
       <c r="H18" s="3">
-        <v>-155600</v>
+        <v>-154500</v>
       </c>
       <c r="I18" s="3">
-        <v>314500</v>
+        <v>312300</v>
       </c>
       <c r="J18" s="3">
-        <v>2134900</v>
+        <v>2120300</v>
       </c>
       <c r="K18" s="3">
         <v>-4469100</v>
@@ -1187,25 +1187,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1196900</v>
+        <v>1188800</v>
       </c>
       <c r="E20" s="3">
-        <v>2077200</v>
+        <v>2063100</v>
       </c>
       <c r="F20" s="3">
-        <v>813900</v>
+        <v>808400</v>
       </c>
       <c r="G20" s="3">
-        <v>175200</v>
+        <v>174000</v>
       </c>
       <c r="H20" s="3">
-        <v>-381900</v>
+        <v>-379300</v>
       </c>
       <c r="I20" s="3">
-        <v>-65300</v>
+        <v>-64800</v>
       </c>
       <c r="J20" s="3">
-        <v>426500</v>
+        <v>423600</v>
       </c>
       <c r="K20" s="3">
         <v>-839800</v>
@@ -1231,26 +1231,26 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
+      <c r="D21" s="3">
+        <v>9525200</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F21" s="3">
-        <v>4343300</v>
+        <v>4285700</v>
       </c>
       <c r="G21" s="3">
-        <v>5178200</v>
+        <v>5100900</v>
       </c>
       <c r="H21" s="3">
-        <v>2477000</v>
+        <v>2423600</v>
       </c>
       <c r="I21" s="3">
-        <v>1297800</v>
+        <v>1276300</v>
       </c>
       <c r="J21" s="3">
-        <v>3621000</v>
+        <v>3583500</v>
       </c>
       <c r="K21" s="3">
         <v>1925400</v>
@@ -1277,25 +1277,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1100100</v>
+        <v>1092600</v>
       </c>
       <c r="E22" s="3">
-        <v>887900</v>
+        <v>881900</v>
       </c>
       <c r="F22" s="3">
-        <v>370000</v>
+        <v>367400</v>
       </c>
       <c r="G22" s="3">
-        <v>322100</v>
+        <v>319900</v>
       </c>
       <c r="H22" s="3">
-        <v>280700</v>
+        <v>278800</v>
       </c>
       <c r="I22" s="3">
-        <v>195900</v>
+        <v>194500</v>
       </c>
       <c r="J22" s="3">
-        <v>324300</v>
+        <v>322000</v>
       </c>
       <c r="K22" s="3">
         <v>991700</v>
@@ -1322,25 +1322,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>4358900</v>
+        <v>4329300</v>
       </c>
       <c r="E23" s="3">
-        <v>778000</v>
+        <v>772700</v>
       </c>
       <c r="F23" s="3">
-        <v>1656100</v>
+        <v>1644800</v>
       </c>
       <c r="G23" s="3">
-        <v>1376400</v>
+        <v>1367100</v>
       </c>
       <c r="H23" s="3">
-        <v>-818300</v>
+        <v>-812700</v>
       </c>
       <c r="I23" s="3">
-        <v>53300</v>
+        <v>53000</v>
       </c>
       <c r="J23" s="3">
-        <v>2237100</v>
+        <v>2221900</v>
       </c>
       <c r="K23" s="3">
         <v>-6300600</v>
@@ -1367,25 +1367,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>2621200</v>
+        <v>2603400</v>
       </c>
       <c r="E24" s="3">
-        <v>-2477600</v>
+        <v>-2460800</v>
       </c>
       <c r="F24" s="3">
-        <v>750800</v>
+        <v>745700</v>
       </c>
       <c r="G24" s="3">
-        <v>409100</v>
+        <v>406300</v>
       </c>
       <c r="H24" s="3">
-        <v>-100100</v>
+        <v>-99400</v>
       </c>
       <c r="I24" s="3">
-        <v>112100</v>
+        <v>111300</v>
       </c>
       <c r="J24" s="3">
-        <v>362300</v>
+        <v>359900</v>
       </c>
       <c r="K24" s="3">
         <v>-350500</v>
@@ -1457,25 +1457,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1737700</v>
+        <v>1725900</v>
       </c>
       <c r="E26" s="3">
-        <v>3255600</v>
+        <v>3233500</v>
       </c>
       <c r="F26" s="3">
-        <v>905300</v>
+        <v>899100</v>
       </c>
       <c r="G26" s="3">
-        <v>967300</v>
+        <v>960700</v>
       </c>
       <c r="H26" s="3">
-        <v>-718100</v>
+        <v>-713300</v>
       </c>
       <c r="I26" s="3">
-        <v>-58800</v>
+        <v>-58400</v>
       </c>
       <c r="J26" s="3">
-        <v>1874800</v>
+        <v>1862000</v>
       </c>
       <c r="K26" s="3">
         <v>-5950100</v>
@@ -1502,25 +1502,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1577700</v>
+        <v>1567000</v>
       </c>
       <c r="E27" s="3">
-        <v>2956400</v>
+        <v>2936300</v>
       </c>
       <c r="F27" s="3">
-        <v>784500</v>
+        <v>779200</v>
       </c>
       <c r="G27" s="3">
-        <v>903100</v>
+        <v>897000</v>
       </c>
       <c r="H27" s="3">
-        <v>-1434100</v>
+        <v>-1424400</v>
       </c>
       <c r="I27" s="3">
-        <v>-861800</v>
+        <v>-855900</v>
       </c>
       <c r="J27" s="3">
-        <v>1423200</v>
+        <v>1413600</v>
       </c>
       <c r="K27" s="3">
         <v>-6195400</v>
@@ -1601,16 +1601,16 @@
         <v>8</v>
       </c>
       <c r="G29" s="3">
-        <v>240500</v>
+        <v>238800</v>
       </c>
       <c r="H29" s="3">
-        <v>10680800</v>
+        <v>10608200</v>
       </c>
       <c r="I29" s="3">
-        <v>1226300</v>
+        <v>1217900</v>
       </c>
       <c r="J29" s="3">
-        <v>644200</v>
+        <v>639800</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1727,25 +1727,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1196900</v>
+        <v>-1188800</v>
       </c>
       <c r="E32" s="3">
-        <v>-2077200</v>
+        <v>-2063100</v>
       </c>
       <c r="F32" s="3">
-        <v>-813900</v>
+        <v>-808400</v>
       </c>
       <c r="G32" s="3">
-        <v>-175200</v>
+        <v>-174000</v>
       </c>
       <c r="H32" s="3">
-        <v>381900</v>
+        <v>379300</v>
       </c>
       <c r="I32" s="3">
-        <v>65300</v>
+        <v>64800</v>
       </c>
       <c r="J32" s="3">
-        <v>-426500</v>
+        <v>-423600</v>
       </c>
       <c r="K32" s="3">
         <v>839800</v>
@@ -1772,25 +1772,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1577700</v>
+        <v>1567000</v>
       </c>
       <c r="E33" s="3">
-        <v>2956400</v>
+        <v>2936300</v>
       </c>
       <c r="F33" s="3">
-        <v>784500</v>
+        <v>779200</v>
       </c>
       <c r="G33" s="3">
-        <v>1143600</v>
+        <v>1135800</v>
       </c>
       <c r="H33" s="3">
-        <v>9246700</v>
+        <v>9183800</v>
       </c>
       <c r="I33" s="3">
-        <v>364500</v>
+        <v>362000</v>
       </c>
       <c r="J33" s="3">
-        <v>2067400</v>
+        <v>2053300</v>
       </c>
       <c r="K33" s="3">
         <v>-6195400</v>
@@ -1862,25 +1862,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1577700</v>
+        <v>1567000</v>
       </c>
       <c r="E35" s="3">
-        <v>2956400</v>
+        <v>2936300</v>
       </c>
       <c r="F35" s="3">
-        <v>784500</v>
+        <v>779200</v>
       </c>
       <c r="G35" s="3">
-        <v>1143600</v>
+        <v>1135800</v>
       </c>
       <c r="H35" s="3">
-        <v>9246700</v>
+        <v>9183800</v>
       </c>
       <c r="I35" s="3">
-        <v>364500</v>
+        <v>362000</v>
       </c>
       <c r="J35" s="3">
-        <v>2067400</v>
+        <v>2053300</v>
       </c>
       <c r="K35" s="3">
         <v>-6195400</v>
@@ -1995,25 +1995,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>7526400</v>
+        <v>7475200</v>
       </c>
       <c r="E41" s="3">
-        <v>7603600</v>
+        <v>7551900</v>
       </c>
       <c r="F41" s="3">
-        <v>6338200</v>
+        <v>6295100</v>
       </c>
       <c r="G41" s="3">
-        <v>5194600</v>
+        <v>5159300</v>
       </c>
       <c r="H41" s="3">
-        <v>6946400</v>
+        <v>6899200</v>
       </c>
       <c r="I41" s="3">
-        <v>3833400</v>
+        <v>3807300</v>
       </c>
       <c r="J41" s="3">
-        <v>4279500</v>
+        <v>4250400</v>
       </c>
       <c r="K41" s="3">
         <v>4965000</v>
@@ -2040,25 +2040,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>8404500</v>
+        <v>8347300</v>
       </c>
       <c r="E42" s="3">
-        <v>14654500</v>
+        <v>14554900</v>
       </c>
       <c r="F42" s="3">
-        <v>8748300</v>
+        <v>8688800</v>
       </c>
       <c r="G42" s="3">
-        <v>4590700</v>
+        <v>4559500</v>
       </c>
       <c r="H42" s="3">
-        <v>3545000</v>
+        <v>3520900</v>
       </c>
       <c r="I42" s="3">
-        <v>3927000</v>
+        <v>3900200</v>
       </c>
       <c r="J42" s="3">
-        <v>5324100</v>
+        <v>5287900</v>
       </c>
       <c r="K42" s="3">
         <v>10660100</v>
@@ -2085,25 +2085,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>11565400</v>
+        <v>11486800</v>
       </c>
       <c r="E43" s="3">
-        <v>20320300</v>
+        <v>20182100</v>
       </c>
       <c r="F43" s="3">
-        <v>20990500</v>
+        <v>20847800</v>
       </c>
       <c r="G43" s="3">
-        <v>9492600</v>
+        <v>9428000</v>
       </c>
       <c r="H43" s="3">
-        <v>10660100</v>
+        <v>10587600</v>
       </c>
       <c r="I43" s="3">
-        <v>5272900</v>
+        <v>5237100</v>
       </c>
       <c r="J43" s="3">
-        <v>8264100</v>
+        <v>8207900</v>
       </c>
       <c r="K43" s="3">
         <v>7273800</v>
@@ -2130,25 +2130,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>2470000</v>
+        <v>2453200</v>
       </c>
       <c r="E44" s="3">
-        <v>4576500</v>
+        <v>4545400</v>
       </c>
       <c r="F44" s="3">
-        <v>3077100</v>
+        <v>3056200</v>
       </c>
       <c r="G44" s="3">
-        <v>3551600</v>
+        <v>3527400</v>
       </c>
       <c r="H44" s="3">
-        <v>3449300</v>
+        <v>3425800</v>
       </c>
       <c r="I44" s="3">
-        <v>1774700</v>
+        <v>1762600</v>
       </c>
       <c r="J44" s="3">
-        <v>2093500</v>
+        <v>2079300</v>
       </c>
       <c r="K44" s="3">
         <v>2135300</v>
@@ -2175,25 +2175,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>28782400</v>
+        <v>28586700</v>
       </c>
       <c r="E45" s="3">
-        <v>57587700</v>
+        <v>57196000</v>
       </c>
       <c r="F45" s="3">
-        <v>73405400</v>
+        <v>72906200</v>
       </c>
       <c r="G45" s="3">
-        <v>25475700</v>
+        <v>25302400</v>
       </c>
       <c r="H45" s="3">
-        <v>31925900</v>
+        <v>31708800</v>
       </c>
       <c r="I45" s="3">
-        <v>52124300</v>
+        <v>51769900</v>
       </c>
       <c r="J45" s="3">
-        <v>5462300</v>
+        <v>5425100</v>
       </c>
       <c r="K45" s="3">
         <v>8048500</v>
@@ -2220,25 +2220,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>58748700</v>
+        <v>58349200</v>
       </c>
       <c r="E46" s="3">
-        <v>104743000</v>
+        <v>104030000</v>
       </c>
       <c r="F46" s="3">
-        <v>112560000</v>
+        <v>111794000</v>
       </c>
       <c r="G46" s="3">
-        <v>29622400</v>
+        <v>29421000</v>
       </c>
       <c r="H46" s="3">
-        <v>30729000</v>
+        <v>30520000</v>
       </c>
       <c r="I46" s="3">
-        <v>66932300</v>
+        <v>66477100</v>
       </c>
       <c r="J46" s="3">
-        <v>25423500</v>
+        <v>25250600</v>
       </c>
       <c r="K46" s="3">
         <v>33082700</v>
@@ -2265,25 +2265,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>10965900</v>
+        <v>10891300</v>
       </c>
       <c r="E47" s="3">
-        <v>9162900</v>
+        <v>9100600</v>
       </c>
       <c r="F47" s="3">
-        <v>9621000</v>
+        <v>9555500</v>
       </c>
       <c r="G47" s="3">
-        <v>8471900</v>
+        <v>8414300</v>
       </c>
       <c r="H47" s="3">
-        <v>8715700</v>
+        <v>8656400</v>
       </c>
       <c r="I47" s="3">
-        <v>2418800</v>
+        <v>2402400</v>
       </c>
       <c r="J47" s="3">
-        <v>4950900</v>
+        <v>4917200</v>
       </c>
       <c r="K47" s="3">
         <v>4974700</v>
@@ -2310,25 +2310,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>31347100</v>
+        <v>31133900</v>
       </c>
       <c r="E48" s="3">
-        <v>25841300</v>
+        <v>25665500</v>
       </c>
       <c r="F48" s="3">
-        <v>21744600</v>
+        <v>21596700</v>
       </c>
       <c r="G48" s="3">
-        <v>38959400</v>
+        <v>38694500</v>
       </c>
       <c r="H48" s="3">
-        <v>41326000</v>
+        <v>41045000</v>
       </c>
       <c r="I48" s="3">
-        <v>13502200</v>
+        <v>13410400</v>
       </c>
       <c r="J48" s="3">
-        <v>27144800</v>
+        <v>26960200</v>
       </c>
       <c r="K48" s="3">
         <v>26602000</v>
@@ -2355,25 +2355,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>10624200</v>
+        <v>10552000</v>
       </c>
       <c r="E49" s="3">
-        <v>6148900</v>
+        <v>6107000</v>
       </c>
       <c r="F49" s="3">
-        <v>6371900</v>
+        <v>6328600</v>
       </c>
       <c r="G49" s="3">
-        <v>10665600</v>
+        <v>10593000</v>
       </c>
       <c r="H49" s="3">
-        <v>10481700</v>
+        <v>10410400</v>
       </c>
       <c r="I49" s="3">
-        <v>2376400</v>
+        <v>2360200</v>
       </c>
       <c r="J49" s="3">
-        <v>13440200</v>
+        <v>13348800</v>
       </c>
       <c r="K49" s="3">
         <v>13826200</v>
@@ -2490,25 +2490,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4190300</v>
+        <v>4161800</v>
       </c>
       <c r="E52" s="3">
-        <v>4858400</v>
+        <v>4825300</v>
       </c>
       <c r="F52" s="3">
-        <v>4549300</v>
+        <v>4518400</v>
       </c>
       <c r="G52" s="3">
-        <v>8213000</v>
+        <v>8157100</v>
       </c>
       <c r="H52" s="3">
-        <v>8313100</v>
+        <v>8256500</v>
       </c>
       <c r="I52" s="3">
-        <v>1935700</v>
+        <v>1922600</v>
       </c>
       <c r="J52" s="3">
-        <v>4183700</v>
+        <v>4155300</v>
       </c>
       <c r="K52" s="3">
         <v>4410500</v>
@@ -2580,25 +2580,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>115876000</v>
+        <v>115088000</v>
       </c>
       <c r="E54" s="3">
-        <v>150754000</v>
+        <v>149729000</v>
       </c>
       <c r="F54" s="3">
-        <v>154846000</v>
+        <v>153793000</v>
       </c>
       <c r="G54" s="3">
-        <v>67072700</v>
+        <v>66616500</v>
       </c>
       <c r="H54" s="3">
-        <v>69648200</v>
+        <v>69174500</v>
       </c>
       <c r="I54" s="3">
-        <v>87165500</v>
+        <v>86572700</v>
       </c>
       <c r="J54" s="3">
-        <v>75143100</v>
+        <v>74632100</v>
       </c>
       <c r="K54" s="3">
         <v>82896200</v>
@@ -2663,25 +2663,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>5564500</v>
+        <v>5526700</v>
       </c>
       <c r="E57" s="3">
-        <v>8121600</v>
+        <v>8066300</v>
       </c>
       <c r="F57" s="3">
-        <v>4818100</v>
+        <v>4785300</v>
       </c>
       <c r="G57" s="3">
-        <v>2597300</v>
+        <v>2579600</v>
       </c>
       <c r="H57" s="3">
-        <v>3250200</v>
+        <v>3228100</v>
       </c>
       <c r="I57" s="3">
-        <v>2643000</v>
+        <v>2625000</v>
       </c>
       <c r="J57" s="3">
-        <v>5524300</v>
+        <v>5486700</v>
       </c>
       <c r="K57" s="3">
         <v>5892600</v>
@@ -2708,25 +2708,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1192600</v>
+        <v>1184400</v>
       </c>
       <c r="E58" s="3">
-        <v>9440400</v>
+        <v>9376200</v>
       </c>
       <c r="F58" s="3">
-        <v>6925800</v>
+        <v>6878700</v>
       </c>
       <c r="G58" s="3">
-        <v>1540700</v>
+        <v>1530300</v>
       </c>
       <c r="H58" s="3">
-        <v>2353600</v>
+        <v>2337600</v>
       </c>
       <c r="I58" s="3">
-        <v>99000</v>
+        <v>98300</v>
       </c>
       <c r="J58" s="3">
-        <v>1869400</v>
+        <v>1856600</v>
       </c>
       <c r="K58" s="3">
         <v>958100</v>
@@ -2753,25 +2753,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>30531000</v>
+        <v>30323400</v>
       </c>
       <c r="E59" s="3">
-        <v>69143300</v>
+        <v>68673100</v>
       </c>
       <c r="F59" s="3">
-        <v>93809500</v>
+        <v>93171500</v>
       </c>
       <c r="G59" s="3">
-        <v>25273300</v>
+        <v>25101400</v>
       </c>
       <c r="H59" s="3">
-        <v>31930300</v>
+        <v>31713100</v>
       </c>
       <c r="I59" s="3">
-        <v>47140800</v>
+        <v>46820200</v>
       </c>
       <c r="J59" s="3">
-        <v>14688300</v>
+        <v>14588400</v>
       </c>
       <c r="K59" s="3">
         <v>24360400</v>
@@ -2798,25 +2798,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>37288100</v>
+        <v>37034500</v>
       </c>
       <c r="E60" s="3">
-        <v>86705200</v>
+        <v>86115600</v>
       </c>
       <c r="F60" s="3">
-        <v>105553000</v>
+        <v>104836000</v>
       </c>
       <c r="G60" s="3">
-        <v>17954700</v>
+        <v>17832600</v>
       </c>
       <c r="H60" s="3">
-        <v>21332200</v>
+        <v>21187100</v>
       </c>
       <c r="I60" s="3">
-        <v>49882900</v>
+        <v>49543600</v>
       </c>
       <c r="J60" s="3">
-        <v>22081900</v>
+        <v>21931700</v>
       </c>
       <c r="K60" s="3">
         <v>31211100</v>
@@ -2843,25 +2843,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>13680700</v>
+        <v>13587600</v>
       </c>
       <c r="E61" s="3">
-        <v>9285800</v>
+        <v>9222700</v>
       </c>
       <c r="F61" s="3">
-        <v>6266400</v>
+        <v>6223800</v>
       </c>
       <c r="G61" s="3">
-        <v>3587500</v>
+        <v>3563100</v>
       </c>
       <c r="H61" s="3">
-        <v>3376400</v>
+        <v>3353400</v>
       </c>
       <c r="I61" s="3">
-        <v>1966200</v>
+        <v>1952800</v>
       </c>
       <c r="J61" s="3">
-        <v>14829700</v>
+        <v>14728900</v>
       </c>
       <c r="K61" s="3">
         <v>16589600</v>
@@ -2888,25 +2888,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>28847700</v>
+        <v>28651500</v>
       </c>
       <c r="E62" s="3">
-        <v>22904500</v>
+        <v>22748700</v>
       </c>
       <c r="F62" s="3">
-        <v>24533400</v>
+        <v>24366500</v>
       </c>
       <c r="G62" s="3">
-        <v>49791500</v>
+        <v>49452800</v>
       </c>
       <c r="H62" s="3">
-        <v>50631500</v>
+        <v>50287100</v>
       </c>
       <c r="I62" s="3">
-        <v>19803400</v>
+        <v>19668700</v>
       </c>
       <c r="J62" s="3">
-        <v>25184100</v>
+        <v>25012800</v>
       </c>
       <c r="K62" s="3">
         <v>26426300</v>
@@ -3068,25 +3068,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>81525900</v>
+        <v>80971400</v>
       </c>
       <c r="E66" s="3">
-        <v>120749000</v>
+        <v>119927000</v>
       </c>
       <c r="F66" s="3">
-        <v>138249000</v>
+        <v>137308000</v>
       </c>
       <c r="G66" s="3">
-        <v>48666400</v>
+        <v>48335400</v>
       </c>
       <c r="H66" s="3">
-        <v>51189700</v>
+        <v>50841500</v>
       </c>
       <c r="I66" s="3">
-        <v>77659900</v>
+        <v>77131700</v>
       </c>
       <c r="J66" s="3">
-        <v>67788600</v>
+        <v>67327600</v>
       </c>
       <c r="K66" s="3">
         <v>79908100</v>
@@ -3312,25 +3312,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>15682800</v>
+        <v>15576100</v>
       </c>
       <c r="E72" s="3">
-        <v>17119100</v>
+        <v>17002700</v>
       </c>
       <c r="F72" s="3">
-        <v>11648100</v>
+        <v>11568900</v>
       </c>
       <c r="G72" s="3">
-        <v>9034500</v>
+        <v>8973100</v>
       </c>
       <c r="H72" s="3">
-        <v>9692800</v>
+        <v>9626900</v>
       </c>
       <c r="I72" s="3">
-        <v>1239300</v>
+        <v>1230900</v>
       </c>
       <c r="J72" s="3">
-        <v>2575500</v>
+        <v>2558000</v>
       </c>
       <c r="K72" s="3">
         <v>-707400</v>
@@ -3492,25 +3492,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>34350200</v>
+        <v>34116600</v>
       </c>
       <c r="E76" s="3">
-        <v>30005400</v>
+        <v>29801400</v>
       </c>
       <c r="F76" s="3">
-        <v>16597900</v>
+        <v>16485000</v>
       </c>
       <c r="G76" s="3">
-        <v>18406300</v>
+        <v>18281100</v>
       </c>
       <c r="H76" s="3">
-        <v>18458500</v>
+        <v>18333000</v>
       </c>
       <c r="I76" s="3">
-        <v>9505600</v>
+        <v>9441000</v>
       </c>
       <c r="J76" s="3">
-        <v>7354500</v>
+        <v>7304500</v>
       </c>
       <c r="K76" s="3">
         <v>2988100</v>
@@ -3632,25 +3632,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1577700</v>
+        <v>1567000</v>
       </c>
       <c r="E81" s="3">
-        <v>2956400</v>
+        <v>2936300</v>
       </c>
       <c r="F81" s="3">
-        <v>784500</v>
+        <v>779200</v>
       </c>
       <c r="G81" s="3">
-        <v>1143600</v>
+        <v>1135800</v>
       </c>
       <c r="H81" s="3">
-        <v>9246700</v>
+        <v>9183800</v>
       </c>
       <c r="I81" s="3">
-        <v>364500</v>
+        <v>362000</v>
       </c>
       <c r="J81" s="3">
-        <v>2067400</v>
+        <v>2053300</v>
       </c>
       <c r="K81" s="3">
         <v>-6195400</v>
@@ -3696,25 +3696,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>4157600</v>
+        <v>4129400</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F83" s="3">
-        <v>2303500</v>
+        <v>2287800</v>
       </c>
       <c r="G83" s="3">
-        <v>3459100</v>
+        <v>3435500</v>
       </c>
       <c r="H83" s="3">
-        <v>2996600</v>
+        <v>2976200</v>
       </c>
       <c r="I83" s="3">
-        <v>1042400</v>
+        <v>1035300</v>
       </c>
       <c r="J83" s="3">
-        <v>1053300</v>
+        <v>1046100</v>
       </c>
       <c r="K83" s="3">
         <v>7237000</v>
@@ -3966,25 +3966,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>4608100</v>
+        <v>4576800</v>
       </c>
       <c r="E89" s="3">
-        <v>2618000</v>
+        <v>2600200</v>
       </c>
       <c r="F89" s="3">
-        <v>7914800</v>
+        <v>7861000</v>
       </c>
       <c r="G89" s="3">
-        <v>4542800</v>
+        <v>4511900</v>
       </c>
       <c r="H89" s="3">
-        <v>-1657200</v>
+        <v>-1645900</v>
       </c>
       <c r="I89" s="3">
-        <v>7233700</v>
+        <v>7184500</v>
       </c>
       <c r="J89" s="3">
-        <v>-1908500</v>
+        <v>-1895500</v>
       </c>
       <c r="K89" s="3">
         <v>2551900</v>
@@ -4030,25 +4030,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-10858100</v>
+        <v>-10784300</v>
       </c>
       <c r="E91" s="3">
-        <v>-4879000</v>
+        <v>-4845900</v>
       </c>
       <c r="F91" s="3">
-        <v>-4101000</v>
+        <v>-4073200</v>
       </c>
       <c r="G91" s="3">
-        <v>-3653800</v>
+        <v>-3629000</v>
       </c>
       <c r="H91" s="3">
-        <v>-1927000</v>
+        <v>-1913900</v>
       </c>
       <c r="I91" s="3">
-        <v>-1355800</v>
+        <v>-1346600</v>
       </c>
       <c r="J91" s="3">
-        <v>-3413400</v>
+        <v>-3390200</v>
       </c>
       <c r="K91" s="3">
         <v>-2504200</v>
@@ -4165,25 +4165,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-3057600</v>
+        <v>-3036800</v>
       </c>
       <c r="E94" s="3">
-        <v>-10763500</v>
+        <v>-10690300</v>
       </c>
       <c r="F94" s="3">
-        <v>-8419700</v>
+        <v>-8362500</v>
       </c>
       <c r="G94" s="3">
-        <v>-4737600</v>
+        <v>-4705400</v>
       </c>
       <c r="H94" s="3">
-        <v>-793200</v>
+        <v>-787800</v>
       </c>
       <c r="I94" s="3">
-        <v>-4792000</v>
+        <v>-4759400</v>
       </c>
       <c r="J94" s="3">
-        <v>2928100</v>
+        <v>2908200</v>
       </c>
       <c r="K94" s="3">
         <v>-4958500</v>
@@ -4229,25 +4229,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1026100</v>
+        <v>-1019100</v>
       </c>
       <c r="E96" s="3">
-        <v>-993400</v>
+        <v>-986700</v>
       </c>
       <c r="F96" s="3">
-        <v>-794300</v>
+        <v>-788900</v>
       </c>
       <c r="G96" s="3">
-        <v>-568000</v>
+        <v>-564100</v>
       </c>
       <c r="H96" s="3">
-        <v>-609300</v>
+        <v>-605200</v>
       </c>
       <c r="I96" s="3">
-        <v>-1115300</v>
+        <v>-1107700</v>
       </c>
       <c r="J96" s="3">
-        <v>-173000</v>
+        <v>-171800</v>
       </c>
       <c r="K96" s="3">
         <v>-441600</v>
@@ -4409,25 +4409,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1694200</v>
+        <v>-1682600</v>
       </c>
       <c r="E100" s="3">
-        <v>9374000</v>
+        <v>9310200</v>
       </c>
       <c r="F100" s="3">
-        <v>1585400</v>
+        <v>1574600</v>
       </c>
       <c r="G100" s="3">
-        <v>1931400</v>
+        <v>1918200</v>
       </c>
       <c r="H100" s="3">
-        <v>243700</v>
+        <v>242100</v>
       </c>
       <c r="I100" s="3">
-        <v>-1077200</v>
+        <v>-1069900</v>
       </c>
       <c r="J100" s="3">
-        <v>-1671300</v>
+        <v>-1660000</v>
       </c>
       <c r="K100" s="3">
         <v>4646000</v>
@@ -4454,25 +4454,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>66400</v>
+        <v>65900</v>
       </c>
       <c r="E101" s="3">
-        <v>37000</v>
+        <v>36700</v>
       </c>
       <c r="F101" s="3">
-        <v>63100</v>
+        <v>62700</v>
       </c>
       <c r="G101" s="3">
-        <v>-37000</v>
+        <v>-36700</v>
       </c>
       <c r="H101" s="3">
-        <v>16300</v>
+        <v>16200</v>
       </c>
       <c r="I101" s="3">
-        <v>14100</v>
+        <v>14000</v>
       </c>
       <c r="J101" s="3">
-        <v>-20700</v>
+        <v>-20500</v>
       </c>
       <c r="K101" s="3">
         <v>-26000</v>
@@ -4499,25 +4499,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-77300</v>
+        <v>-76700</v>
       </c>
       <c r="E102" s="3">
-        <v>1265500</v>
+        <v>1256900</v>
       </c>
       <c r="F102" s="3">
-        <v>1143600</v>
+        <v>1135800</v>
       </c>
       <c r="G102" s="3">
-        <v>1699600</v>
+        <v>1688100</v>
       </c>
       <c r="H102" s="3">
-        <v>-2190300</v>
+        <v>-2175400</v>
       </c>
       <c r="I102" s="3">
-        <v>1378600</v>
+        <v>1369200</v>
       </c>
       <c r="J102" s="3">
-        <v>-672400</v>
+        <v>-667900</v>
       </c>
       <c r="K102" s="3">
         <v>2213400</v>

--- a/AAII_Financials/Yearly/RWEOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RWEOY_YR_FIN.xlsx
@@ -728,25 +728,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>30871300</v>
+        <v>31639700</v>
       </c>
       <c r="E8" s="3">
-        <v>41462100</v>
+        <v>42494200</v>
       </c>
       <c r="F8" s="3">
-        <v>26553900</v>
+        <v>27214800</v>
       </c>
       <c r="G8" s="3">
-        <v>14792600</v>
+        <v>15160800</v>
       </c>
       <c r="H8" s="3">
-        <v>14184200</v>
+        <v>14537300</v>
       </c>
       <c r="I8" s="3">
-        <v>14487900</v>
+        <v>14848500</v>
       </c>
       <c r="J8" s="3">
-        <v>14937400</v>
+        <v>15309200</v>
       </c>
       <c r="K8" s="3">
         <v>47295200</v>
@@ -773,25 +773,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>21597800</v>
+        <v>22135400</v>
       </c>
       <c r="E9" s="3">
-        <v>33774000</v>
+        <v>34614700</v>
       </c>
       <c r="F9" s="3">
-        <v>19118700</v>
+        <v>19594600</v>
       </c>
       <c r="G9" s="3">
-        <v>10504400</v>
+        <v>10765900</v>
       </c>
       <c r="H9" s="3">
-        <v>9705800</v>
+        <v>9947400</v>
       </c>
       <c r="I9" s="3">
-        <v>10756200</v>
+        <v>11023900</v>
       </c>
       <c r="J9" s="3">
-        <v>10771300</v>
+        <v>11039400</v>
       </c>
       <c r="K9" s="3">
         <v>35950400</v>
@@ -818,25 +818,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>9273500</v>
+        <v>9504300</v>
       </c>
       <c r="E10" s="3">
-        <v>7688100</v>
+        <v>7879500</v>
       </c>
       <c r="F10" s="3">
-        <v>7435200</v>
+        <v>7620300</v>
       </c>
       <c r="G10" s="3">
-        <v>4288200</v>
+        <v>4395000</v>
       </c>
       <c r="H10" s="3">
-        <v>4478400</v>
+        <v>4589900</v>
       </c>
       <c r="I10" s="3">
-        <v>3731700</v>
+        <v>3824500</v>
       </c>
       <c r="J10" s="3">
-        <v>4166100</v>
+        <v>4269800</v>
       </c>
       <c r="K10" s="3">
         <v>11344800</v>
@@ -972,25 +972,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1595100</v>
+        <v>1634800</v>
       </c>
       <c r="E14" s="3">
-        <v>-2009000</v>
+        <v>-2059000</v>
       </c>
       <c r="F14" s="3">
-        <v>591100</v>
+        <v>605900</v>
       </c>
       <c r="G14" s="3">
-        <v>1746400</v>
+        <v>1789900</v>
       </c>
       <c r="H14" s="3">
-        <v>1585400</v>
+        <v>1624800</v>
       </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
       <c r="J14" s="3">
-        <v>421500</v>
+        <v>432000</v>
       </c>
       <c r="K14" s="3">
         <v>4495200</v>
@@ -1017,25 +1017,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2055500</v>
+        <v>2106700</v>
       </c>
       <c r="E15" s="3">
-        <v>1761500</v>
+        <v>1805400</v>
       </c>
       <c r="F15" s="3">
-        <v>1535700</v>
+        <v>1573900</v>
       </c>
       <c r="G15" s="3">
-        <v>1538900</v>
+        <v>1577200</v>
       </c>
       <c r="H15" s="3">
-        <v>1294700</v>
+        <v>1326900</v>
       </c>
       <c r="I15" s="3">
-        <v>973700</v>
+        <v>997900</v>
       </c>
       <c r="J15" s="3">
-        <v>1028800</v>
+        <v>1054400</v>
       </c>
       <c r="K15" s="3">
         <v>2459700</v>
@@ -1078,25 +1078,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>26638200</v>
+        <v>27301200</v>
       </c>
       <c r="E17" s="3">
-        <v>41870600</v>
+        <v>42912900</v>
       </c>
       <c r="F17" s="3">
-        <v>25350000</v>
+        <v>25981000</v>
       </c>
       <c r="G17" s="3">
-        <v>13279600</v>
+        <v>13610200</v>
       </c>
       <c r="H17" s="3">
-        <v>14338700</v>
+        <v>14695600</v>
       </c>
       <c r="I17" s="3">
-        <v>14175500</v>
+        <v>14528400</v>
       </c>
       <c r="J17" s="3">
-        <v>12817100</v>
+        <v>13136100</v>
       </c>
       <c r="K17" s="3">
         <v>51764300</v>
@@ -1123,25 +1123,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4233100</v>
+        <v>4338500</v>
       </c>
       <c r="E18" s="3">
-        <v>-408500</v>
+        <v>-418700</v>
       </c>
       <c r="F18" s="3">
-        <v>1203900</v>
+        <v>1233900</v>
       </c>
       <c r="G18" s="3">
-        <v>1513000</v>
+        <v>1550600</v>
       </c>
       <c r="H18" s="3">
-        <v>-154500</v>
+        <v>-158400</v>
       </c>
       <c r="I18" s="3">
-        <v>312300</v>
+        <v>320100</v>
       </c>
       <c r="J18" s="3">
-        <v>2120300</v>
+        <v>2173100</v>
       </c>
       <c r="K18" s="3">
         <v>-4469100</v>
@@ -1187,25 +1187,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1188800</v>
+        <v>1218400</v>
       </c>
       <c r="E20" s="3">
-        <v>2063100</v>
+        <v>2114400</v>
       </c>
       <c r="F20" s="3">
-        <v>808400</v>
+        <v>828500</v>
       </c>
       <c r="G20" s="3">
-        <v>174000</v>
+        <v>178300</v>
       </c>
       <c r="H20" s="3">
-        <v>-379300</v>
+        <v>-388800</v>
       </c>
       <c r="I20" s="3">
-        <v>-64800</v>
+        <v>-66500</v>
       </c>
       <c r="J20" s="3">
-        <v>423600</v>
+        <v>434200</v>
       </c>
       <c r="K20" s="3">
         <v>-839800</v>
@@ -1232,25 +1232,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>9525200</v>
+        <v>9788200</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F21" s="3">
-        <v>4285700</v>
+        <v>4406700</v>
       </c>
       <c r="G21" s="3">
-        <v>5100900</v>
+        <v>5249400</v>
       </c>
       <c r="H21" s="3">
-        <v>2423600</v>
+        <v>2502600</v>
       </c>
       <c r="I21" s="3">
-        <v>1276300</v>
+        <v>1314500</v>
       </c>
       <c r="J21" s="3">
-        <v>3583500</v>
+        <v>3679300</v>
       </c>
       <c r="K21" s="3">
         <v>1925400</v>
@@ -1277,25 +1277,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1092600</v>
+        <v>1119800</v>
       </c>
       <c r="E22" s="3">
-        <v>881900</v>
+        <v>903800</v>
       </c>
       <c r="F22" s="3">
-        <v>367400</v>
+        <v>376600</v>
       </c>
       <c r="G22" s="3">
-        <v>319900</v>
+        <v>327800</v>
       </c>
       <c r="H22" s="3">
-        <v>278800</v>
+        <v>285800</v>
       </c>
       <c r="I22" s="3">
-        <v>194500</v>
+        <v>199400</v>
       </c>
       <c r="J22" s="3">
-        <v>322000</v>
+        <v>330100</v>
       </c>
       <c r="K22" s="3">
         <v>991700</v>
@@ -1322,25 +1322,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>4329300</v>
+        <v>4437000</v>
       </c>
       <c r="E23" s="3">
-        <v>772700</v>
+        <v>791900</v>
       </c>
       <c r="F23" s="3">
-        <v>1644800</v>
+        <v>1685800</v>
       </c>
       <c r="G23" s="3">
-        <v>1367100</v>
+        <v>1401100</v>
       </c>
       <c r="H23" s="3">
-        <v>-812700</v>
+        <v>-832900</v>
       </c>
       <c r="I23" s="3">
-        <v>53000</v>
+        <v>54300</v>
       </c>
       <c r="J23" s="3">
-        <v>2221900</v>
+        <v>2277200</v>
       </c>
       <c r="K23" s="3">
         <v>-6300600</v>
@@ -1367,25 +1367,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>2603400</v>
+        <v>2668200</v>
       </c>
       <c r="E24" s="3">
-        <v>-2460800</v>
+        <v>-2522000</v>
       </c>
       <c r="F24" s="3">
-        <v>745700</v>
+        <v>764200</v>
       </c>
       <c r="G24" s="3">
-        <v>406300</v>
+        <v>416500</v>
       </c>
       <c r="H24" s="3">
-        <v>-99400</v>
+        <v>-101900</v>
       </c>
       <c r="I24" s="3">
-        <v>111300</v>
+        <v>114100</v>
       </c>
       <c r="J24" s="3">
-        <v>359900</v>
+        <v>368800</v>
       </c>
       <c r="K24" s="3">
         <v>-350500</v>
@@ -1457,25 +1457,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1725900</v>
+        <v>1768800</v>
       </c>
       <c r="E26" s="3">
-        <v>3233500</v>
+        <v>3313900</v>
       </c>
       <c r="F26" s="3">
-        <v>899100</v>
+        <v>921500</v>
       </c>
       <c r="G26" s="3">
-        <v>960700</v>
+        <v>984700</v>
       </c>
       <c r="H26" s="3">
-        <v>-713300</v>
+        <v>-731000</v>
       </c>
       <c r="I26" s="3">
-        <v>-58400</v>
+        <v>-59800</v>
       </c>
       <c r="J26" s="3">
-        <v>1862000</v>
+        <v>1908400</v>
       </c>
       <c r="K26" s="3">
         <v>-5950100</v>
@@ -1502,25 +1502,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1567000</v>
+        <v>1606000</v>
       </c>
       <c r="E27" s="3">
-        <v>2936300</v>
+        <v>3009300</v>
       </c>
       <c r="F27" s="3">
-        <v>779200</v>
+        <v>798600</v>
       </c>
       <c r="G27" s="3">
-        <v>897000</v>
+        <v>919300</v>
       </c>
       <c r="H27" s="3">
-        <v>-1424400</v>
+        <v>-1459800</v>
       </c>
       <c r="I27" s="3">
-        <v>-855900</v>
+        <v>-877200</v>
       </c>
       <c r="J27" s="3">
-        <v>1413600</v>
+        <v>1448700</v>
       </c>
       <c r="K27" s="3">
         <v>-6195400</v>
@@ -1601,16 +1601,16 @@
         <v>8</v>
       </c>
       <c r="G29" s="3">
-        <v>238800</v>
+        <v>244800</v>
       </c>
       <c r="H29" s="3">
-        <v>10608200</v>
+        <v>10872200</v>
       </c>
       <c r="I29" s="3">
-        <v>1217900</v>
+        <v>1248300</v>
       </c>
       <c r="J29" s="3">
-        <v>639800</v>
+        <v>655700</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1727,25 +1727,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1188800</v>
+        <v>-1218400</v>
       </c>
       <c r="E32" s="3">
-        <v>-2063100</v>
+        <v>-2114400</v>
       </c>
       <c r="F32" s="3">
-        <v>-808400</v>
+        <v>-828500</v>
       </c>
       <c r="G32" s="3">
-        <v>-174000</v>
+        <v>-178300</v>
       </c>
       <c r="H32" s="3">
-        <v>379300</v>
+        <v>388800</v>
       </c>
       <c r="I32" s="3">
-        <v>64800</v>
+        <v>66500</v>
       </c>
       <c r="J32" s="3">
-        <v>-423600</v>
+        <v>-434200</v>
       </c>
       <c r="K32" s="3">
         <v>839800</v>
@@ -1772,25 +1772,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1567000</v>
+        <v>1606000</v>
       </c>
       <c r="E33" s="3">
-        <v>2936300</v>
+        <v>3009300</v>
       </c>
       <c r="F33" s="3">
-        <v>779200</v>
+        <v>798600</v>
       </c>
       <c r="G33" s="3">
-        <v>1135800</v>
+        <v>1164100</v>
       </c>
       <c r="H33" s="3">
-        <v>9183800</v>
+        <v>9412400</v>
       </c>
       <c r="I33" s="3">
-        <v>362000</v>
+        <v>371000</v>
       </c>
       <c r="J33" s="3">
-        <v>2053300</v>
+        <v>2104400</v>
       </c>
       <c r="K33" s="3">
         <v>-6195400</v>
@@ -1862,25 +1862,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1567000</v>
+        <v>1606000</v>
       </c>
       <c r="E35" s="3">
-        <v>2936300</v>
+        <v>3009300</v>
       </c>
       <c r="F35" s="3">
-        <v>779200</v>
+        <v>798600</v>
       </c>
       <c r="G35" s="3">
-        <v>1135800</v>
+        <v>1164100</v>
       </c>
       <c r="H35" s="3">
-        <v>9183800</v>
+        <v>9412400</v>
       </c>
       <c r="I35" s="3">
-        <v>362000</v>
+        <v>371000</v>
       </c>
       <c r="J35" s="3">
-        <v>2053300</v>
+        <v>2104400</v>
       </c>
       <c r="K35" s="3">
         <v>-6195400</v>
@@ -1995,25 +1995,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>7475200</v>
+        <v>7661300</v>
       </c>
       <c r="E41" s="3">
-        <v>7551900</v>
+        <v>7739900</v>
       </c>
       <c r="F41" s="3">
-        <v>6295100</v>
+        <v>6451800</v>
       </c>
       <c r="G41" s="3">
-        <v>5159300</v>
+        <v>5287700</v>
       </c>
       <c r="H41" s="3">
-        <v>6899200</v>
+        <v>7070900</v>
       </c>
       <c r="I41" s="3">
-        <v>3807300</v>
+        <v>3902100</v>
       </c>
       <c r="J41" s="3">
-        <v>4250400</v>
+        <v>4356200</v>
       </c>
       <c r="K41" s="3">
         <v>4965000</v>
@@ -2040,25 +2040,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>8347300</v>
+        <v>8555100</v>
       </c>
       <c r="E42" s="3">
-        <v>14554900</v>
+        <v>14917200</v>
       </c>
       <c r="F42" s="3">
-        <v>8688800</v>
+        <v>8905100</v>
       </c>
       <c r="G42" s="3">
-        <v>4559500</v>
+        <v>4673000</v>
       </c>
       <c r="H42" s="3">
-        <v>3520900</v>
+        <v>3608600</v>
       </c>
       <c r="I42" s="3">
-        <v>3900200</v>
+        <v>3997300</v>
       </c>
       <c r="J42" s="3">
-        <v>5287900</v>
+        <v>5419500</v>
       </c>
       <c r="K42" s="3">
         <v>10660100</v>
@@ -2085,25 +2085,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>11486800</v>
+        <v>20198200</v>
       </c>
       <c r="E43" s="3">
-        <v>20182100</v>
+        <v>20684400</v>
       </c>
       <c r="F43" s="3">
-        <v>20847800</v>
+        <v>21366700</v>
       </c>
       <c r="G43" s="3">
-        <v>9428000</v>
+        <v>9662700</v>
       </c>
       <c r="H43" s="3">
-        <v>10587600</v>
+        <v>10851200</v>
       </c>
       <c r="I43" s="3">
-        <v>5237100</v>
+        <v>5367400</v>
       </c>
       <c r="J43" s="3">
-        <v>8207900</v>
+        <v>8412200</v>
       </c>
       <c r="K43" s="3">
         <v>7273800</v>
@@ -2130,25 +2130,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>2453200</v>
+        <v>5028500</v>
       </c>
       <c r="E44" s="3">
-        <v>4545400</v>
+        <v>4658600</v>
       </c>
       <c r="F44" s="3">
-        <v>3056200</v>
+        <v>3132300</v>
       </c>
       <c r="G44" s="3">
-        <v>3527400</v>
+        <v>3615200</v>
       </c>
       <c r="H44" s="3">
-        <v>3425800</v>
+        <v>3511100</v>
       </c>
       <c r="I44" s="3">
-        <v>1762600</v>
+        <v>1806500</v>
       </c>
       <c r="J44" s="3">
-        <v>2079300</v>
+        <v>2131000</v>
       </c>
       <c r="K44" s="3">
         <v>2135300</v>
@@ -2175,25 +2175,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>28586700</v>
+        <v>61968000</v>
       </c>
       <c r="E45" s="3">
-        <v>57196000</v>
+        <v>58619700</v>
       </c>
       <c r="F45" s="3">
-        <v>72906200</v>
+        <v>74720900</v>
       </c>
       <c r="G45" s="3">
-        <v>25302400</v>
+        <v>25932200</v>
       </c>
       <c r="H45" s="3">
-        <v>31708800</v>
+        <v>32498100</v>
       </c>
       <c r="I45" s="3">
-        <v>51769900</v>
+        <v>53058500</v>
       </c>
       <c r="J45" s="3">
-        <v>5425100</v>
+        <v>5560200</v>
       </c>
       <c r="K45" s="3">
         <v>8048500</v>
@@ -2220,25 +2220,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>58349200</v>
+        <v>59825900</v>
       </c>
       <c r="E46" s="3">
-        <v>104030000</v>
+        <v>106620000</v>
       </c>
       <c r="F46" s="3">
-        <v>111794000</v>
+        <v>114577000</v>
       </c>
       <c r="G46" s="3">
-        <v>29421000</v>
+        <v>30153300</v>
       </c>
       <c r="H46" s="3">
-        <v>30520000</v>
+        <v>31279700</v>
       </c>
       <c r="I46" s="3">
-        <v>66477100</v>
+        <v>68131800</v>
       </c>
       <c r="J46" s="3">
-        <v>25250600</v>
+        <v>25879100</v>
       </c>
       <c r="K46" s="3">
         <v>33082700</v>
@@ -2265,25 +2265,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>10891300</v>
+        <v>11158000</v>
       </c>
       <c r="E47" s="3">
-        <v>9100600</v>
+        <v>9327100</v>
       </c>
       <c r="F47" s="3">
-        <v>9555500</v>
+        <v>9793400</v>
       </c>
       <c r="G47" s="3">
-        <v>8414300</v>
+        <v>8623800</v>
       </c>
       <c r="H47" s="3">
-        <v>8656400</v>
+        <v>8871900</v>
       </c>
       <c r="I47" s="3">
-        <v>2402400</v>
+        <v>2462200</v>
       </c>
       <c r="J47" s="3">
-        <v>4917200</v>
+        <v>5039600</v>
       </c>
       <c r="K47" s="3">
         <v>4974700</v>
@@ -2310,25 +2310,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>31133900</v>
+        <v>63816600</v>
       </c>
       <c r="E48" s="3">
-        <v>25665500</v>
+        <v>26304400</v>
       </c>
       <c r="F48" s="3">
-        <v>21596700</v>
+        <v>22134300</v>
       </c>
       <c r="G48" s="3">
-        <v>38694500</v>
+        <v>39657600</v>
       </c>
       <c r="H48" s="3">
-        <v>41045000</v>
+        <v>42066600</v>
       </c>
       <c r="I48" s="3">
-        <v>13410400</v>
+        <v>13744200</v>
       </c>
       <c r="J48" s="3">
-        <v>26960200</v>
+        <v>27631300</v>
       </c>
       <c r="K48" s="3">
         <v>26602000</v>
@@ -2355,25 +2355,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>10552000</v>
+        <v>21654700</v>
       </c>
       <c r="E49" s="3">
-        <v>6107000</v>
+        <v>6259000</v>
       </c>
       <c r="F49" s="3">
-        <v>6328600</v>
+        <v>6486100</v>
       </c>
       <c r="G49" s="3">
-        <v>10593000</v>
+        <v>10856700</v>
       </c>
       <c r="H49" s="3">
-        <v>10410400</v>
+        <v>10669500</v>
       </c>
       <c r="I49" s="3">
-        <v>2360200</v>
+        <v>2419000</v>
       </c>
       <c r="J49" s="3">
-        <v>13348800</v>
+        <v>13681100</v>
       </c>
       <c r="K49" s="3">
         <v>13826200</v>
@@ -2490,25 +2490,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>4161800</v>
+        <v>8281500</v>
       </c>
       <c r="E52" s="3">
-        <v>4825300</v>
+        <v>4945400</v>
       </c>
       <c r="F52" s="3">
-        <v>4518400</v>
+        <v>4630900</v>
       </c>
       <c r="G52" s="3">
-        <v>8157100</v>
+        <v>8360200</v>
       </c>
       <c r="H52" s="3">
-        <v>8256500</v>
+        <v>8462100</v>
       </c>
       <c r="I52" s="3">
-        <v>1922600</v>
+        <v>1970400</v>
       </c>
       <c r="J52" s="3">
-        <v>4155300</v>
+        <v>4258700</v>
       </c>
       <c r="K52" s="3">
         <v>4410500</v>
@@ -2580,25 +2580,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>115088000</v>
+        <v>117973000</v>
       </c>
       <c r="E54" s="3">
-        <v>149729000</v>
+        <v>153456000</v>
       </c>
       <c r="F54" s="3">
-        <v>153793000</v>
+        <v>157621000</v>
       </c>
       <c r="G54" s="3">
-        <v>66616500</v>
+        <v>68274700</v>
       </c>
       <c r="H54" s="3">
-        <v>69174500</v>
+        <v>70896400</v>
       </c>
       <c r="I54" s="3">
-        <v>86572700</v>
+        <v>88727600</v>
       </c>
       <c r="J54" s="3">
-        <v>74632100</v>
+        <v>76489700</v>
       </c>
       <c r="K54" s="3">
         <v>82896200</v>
@@ -2663,25 +2663,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>5526700</v>
+        <v>5664300</v>
       </c>
       <c r="E57" s="3">
-        <v>8066300</v>
+        <v>8267100</v>
       </c>
       <c r="F57" s="3">
-        <v>4785300</v>
+        <v>4904500</v>
       </c>
       <c r="G57" s="3">
-        <v>2579600</v>
+        <v>2643800</v>
       </c>
       <c r="H57" s="3">
-        <v>3228100</v>
+        <v>3308400</v>
       </c>
       <c r="I57" s="3">
-        <v>2625000</v>
+        <v>2690400</v>
       </c>
       <c r="J57" s="3">
-        <v>5486700</v>
+        <v>5623300</v>
       </c>
       <c r="K57" s="3">
         <v>5892600</v>
@@ -2708,25 +2708,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1184400</v>
+        <v>4496900</v>
       </c>
       <c r="E58" s="3">
-        <v>9376200</v>
+        <v>9609500</v>
       </c>
       <c r="F58" s="3">
-        <v>6878700</v>
+        <v>7049900</v>
       </c>
       <c r="G58" s="3">
-        <v>1530300</v>
+        <v>1568400</v>
       </c>
       <c r="H58" s="3">
-        <v>2337600</v>
+        <v>2395700</v>
       </c>
       <c r="I58" s="3">
-        <v>98300</v>
+        <v>100800</v>
       </c>
       <c r="J58" s="3">
-        <v>1856600</v>
+        <v>1902900</v>
       </c>
       <c r="K58" s="3">
         <v>958100</v>
@@ -2753,25 +2753,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>30323400</v>
+        <v>52539000</v>
       </c>
       <c r="E59" s="3">
-        <v>68673100</v>
+        <v>70382400</v>
       </c>
       <c r="F59" s="3">
-        <v>93171500</v>
+        <v>95490600</v>
       </c>
       <c r="G59" s="3">
-        <v>25101400</v>
+        <v>25726200</v>
       </c>
       <c r="H59" s="3">
-        <v>31713100</v>
+        <v>32502500</v>
       </c>
       <c r="I59" s="3">
-        <v>46820200</v>
+        <v>47985700</v>
       </c>
       <c r="J59" s="3">
-        <v>14588400</v>
+        <v>14951500</v>
       </c>
       <c r="K59" s="3">
         <v>24360400</v>
@@ -2798,25 +2798,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>37034500</v>
+        <v>37956300</v>
       </c>
       <c r="E60" s="3">
-        <v>86115600</v>
+        <v>88259100</v>
       </c>
       <c r="F60" s="3">
-        <v>104836000</v>
+        <v>107445000</v>
       </c>
       <c r="G60" s="3">
-        <v>17832600</v>
+        <v>18276500</v>
       </c>
       <c r="H60" s="3">
-        <v>21187100</v>
+        <v>21714500</v>
       </c>
       <c r="I60" s="3">
-        <v>49543600</v>
+        <v>50776800</v>
       </c>
       <c r="J60" s="3">
-        <v>21931700</v>
+        <v>22477600</v>
       </c>
       <c r="K60" s="3">
         <v>31211100</v>
@@ -2843,25 +2843,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>13587600</v>
+        <v>15577300</v>
       </c>
       <c r="E61" s="3">
-        <v>9222700</v>
+        <v>9452300</v>
       </c>
       <c r="F61" s="3">
-        <v>6223800</v>
+        <v>6378700</v>
       </c>
       <c r="G61" s="3">
-        <v>3563100</v>
+        <v>3651800</v>
       </c>
       <c r="H61" s="3">
-        <v>3353400</v>
+        <v>3436900</v>
       </c>
       <c r="I61" s="3">
-        <v>1952800</v>
+        <v>2001400</v>
       </c>
       <c r="J61" s="3">
-        <v>14728900</v>
+        <v>15095500</v>
       </c>
       <c r="K61" s="3">
         <v>16589600</v>
@@ -2888,25 +2888,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>28651500</v>
+        <v>51108000</v>
       </c>
       <c r="E62" s="3">
-        <v>22748700</v>
+        <v>23315000</v>
       </c>
       <c r="F62" s="3">
-        <v>24366500</v>
+        <v>24973100</v>
       </c>
       <c r="G62" s="3">
-        <v>49452800</v>
+        <v>50683800</v>
       </c>
       <c r="H62" s="3">
-        <v>50287100</v>
+        <v>51538800</v>
       </c>
       <c r="I62" s="3">
-        <v>19668700</v>
+        <v>20158300</v>
       </c>
       <c r="J62" s="3">
-        <v>25012800</v>
+        <v>25635400</v>
       </c>
       <c r="K62" s="3">
         <v>26426300</v>
@@ -3068,25 +3068,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>80971400</v>
+        <v>82986900</v>
       </c>
       <c r="E66" s="3">
-        <v>119927000</v>
+        <v>122913000</v>
       </c>
       <c r="F66" s="3">
-        <v>137308000</v>
+        <v>140726000</v>
       </c>
       <c r="G66" s="3">
-        <v>48335400</v>
+        <v>49538500</v>
       </c>
       <c r="H66" s="3">
-        <v>50841500</v>
+        <v>52107000</v>
       </c>
       <c r="I66" s="3">
-        <v>77131700</v>
+        <v>79051600</v>
       </c>
       <c r="J66" s="3">
-        <v>67327600</v>
+        <v>69003500</v>
       </c>
       <c r="K66" s="3">
         <v>79908100</v>
@@ -3312,25 +3312,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>15576100</v>
+        <v>15963800</v>
       </c>
       <c r="E72" s="3">
-        <v>17002700</v>
+        <v>17425900</v>
       </c>
       <c r="F72" s="3">
-        <v>11568900</v>
+        <v>11856900</v>
       </c>
       <c r="G72" s="3">
-        <v>8973100</v>
+        <v>9196400</v>
       </c>
       <c r="H72" s="3">
-        <v>9626900</v>
+        <v>9866500</v>
       </c>
       <c r="I72" s="3">
-        <v>1230900</v>
+        <v>1261600</v>
       </c>
       <c r="J72" s="3">
-        <v>2558000</v>
+        <v>2621700</v>
       </c>
       <c r="K72" s="3">
         <v>-707400</v>
@@ -3492,25 +3492,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>34116600</v>
+        <v>34985800</v>
       </c>
       <c r="E76" s="3">
-        <v>29801400</v>
+        <v>30543200</v>
       </c>
       <c r="F76" s="3">
-        <v>16485000</v>
+        <v>16895300</v>
       </c>
       <c r="G76" s="3">
-        <v>18281100</v>
+        <v>18736200</v>
       </c>
       <c r="H76" s="3">
-        <v>18333000</v>
+        <v>18789300</v>
       </c>
       <c r="I76" s="3">
-        <v>9441000</v>
+        <v>9676000</v>
       </c>
       <c r="J76" s="3">
-        <v>7304500</v>
+        <v>7486300</v>
       </c>
       <c r="K76" s="3">
         <v>2988100</v>
@@ -3632,25 +3632,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1567000</v>
+        <v>1606000</v>
       </c>
       <c r="E81" s="3">
-        <v>2936300</v>
+        <v>3009300</v>
       </c>
       <c r="F81" s="3">
-        <v>779200</v>
+        <v>798600</v>
       </c>
       <c r="G81" s="3">
-        <v>1135800</v>
+        <v>1164100</v>
       </c>
       <c r="H81" s="3">
-        <v>9183800</v>
+        <v>9412400</v>
       </c>
       <c r="I81" s="3">
-        <v>362000</v>
+        <v>371000</v>
       </c>
       <c r="J81" s="3">
-        <v>2053300</v>
+        <v>2104400</v>
       </c>
       <c r="K81" s="3">
         <v>-6195400</v>
@@ -3696,25 +3696,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>4129400</v>
+        <v>4232100</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F83" s="3">
-        <v>2287800</v>
+        <v>2344800</v>
       </c>
       <c r="G83" s="3">
-        <v>3435500</v>
+        <v>3521100</v>
       </c>
       <c r="H83" s="3">
-        <v>2976200</v>
+        <v>3050300</v>
       </c>
       <c r="I83" s="3">
-        <v>1035300</v>
+        <v>1061100</v>
       </c>
       <c r="J83" s="3">
-        <v>1046100</v>
+        <v>1072200</v>
       </c>
       <c r="K83" s="3">
         <v>7237000</v>
@@ -3966,25 +3966,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>4576800</v>
+        <v>4690700</v>
       </c>
       <c r="E89" s="3">
-        <v>2600200</v>
+        <v>2664900</v>
       </c>
       <c r="F89" s="3">
-        <v>7861000</v>
+        <v>8056700</v>
       </c>
       <c r="G89" s="3">
-        <v>4511900</v>
+        <v>4624200</v>
       </c>
       <c r="H89" s="3">
-        <v>-1645900</v>
+        <v>-1686900</v>
       </c>
       <c r="I89" s="3">
-        <v>7184500</v>
+        <v>7363300</v>
       </c>
       <c r="J89" s="3">
-        <v>-1895500</v>
+        <v>-1942700</v>
       </c>
       <c r="K89" s="3">
         <v>2551900</v>
@@ -4030,25 +4030,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-10784300</v>
+        <v>-11052700</v>
       </c>
       <c r="E91" s="3">
-        <v>-4845900</v>
+        <v>-4966500</v>
       </c>
       <c r="F91" s="3">
-        <v>-4073200</v>
+        <v>-4174500</v>
       </c>
       <c r="G91" s="3">
-        <v>-3629000</v>
+        <v>-3719300</v>
       </c>
       <c r="H91" s="3">
-        <v>-1913900</v>
+        <v>-1961600</v>
       </c>
       <c r="I91" s="3">
-        <v>-1346600</v>
+        <v>-1380100</v>
       </c>
       <c r="J91" s="3">
-        <v>-3390200</v>
+        <v>-3474500</v>
       </c>
       <c r="K91" s="3">
         <v>-2504200</v>
@@ -4165,25 +4165,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-3036800</v>
+        <v>-3112400</v>
       </c>
       <c r="E94" s="3">
-        <v>-10690300</v>
+        <v>-10956400</v>
       </c>
       <c r="F94" s="3">
-        <v>-8362500</v>
+        <v>-8570600</v>
       </c>
       <c r="G94" s="3">
-        <v>-4705400</v>
+        <v>-4822500</v>
       </c>
       <c r="H94" s="3">
-        <v>-787800</v>
+        <v>-807400</v>
       </c>
       <c r="I94" s="3">
-        <v>-4759400</v>
+        <v>-4877900</v>
       </c>
       <c r="J94" s="3">
-        <v>2908200</v>
+        <v>2980600</v>
       </c>
       <c r="K94" s="3">
         <v>-4958500</v>
@@ -4229,25 +4229,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1019100</v>
+        <v>-1044500</v>
       </c>
       <c r="E96" s="3">
-        <v>-986700</v>
+        <v>-1011200</v>
       </c>
       <c r="F96" s="3">
-        <v>-788900</v>
+        <v>-808500</v>
       </c>
       <c r="G96" s="3">
-        <v>-564100</v>
+        <v>-578200</v>
       </c>
       <c r="H96" s="3">
-        <v>-605200</v>
+        <v>-620300</v>
       </c>
       <c r="I96" s="3">
-        <v>-1107700</v>
+        <v>-1135300</v>
       </c>
       <c r="J96" s="3">
-        <v>-171800</v>
+        <v>-176100</v>
       </c>
       <c r="K96" s="3">
         <v>-441600</v>
@@ -4409,25 +4409,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1682600</v>
+        <v>-1724500</v>
       </c>
       <c r="E100" s="3">
-        <v>9310200</v>
+        <v>9542000</v>
       </c>
       <c r="F100" s="3">
-        <v>1574600</v>
+        <v>1613800</v>
       </c>
       <c r="G100" s="3">
-        <v>1918200</v>
+        <v>1966000</v>
       </c>
       <c r="H100" s="3">
-        <v>242100</v>
+        <v>248100</v>
       </c>
       <c r="I100" s="3">
-        <v>-1069900</v>
+        <v>-1096500</v>
       </c>
       <c r="J100" s="3">
-        <v>-1660000</v>
+        <v>-1701300</v>
       </c>
       <c r="K100" s="3">
         <v>4646000</v>
@@ -4454,25 +4454,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>65900</v>
+        <v>67600</v>
       </c>
       <c r="E101" s="3">
-        <v>36700</v>
+        <v>37700</v>
       </c>
       <c r="F101" s="3">
-        <v>62700</v>
+        <v>64200</v>
       </c>
       <c r="G101" s="3">
-        <v>-36700</v>
+        <v>-37700</v>
       </c>
       <c r="H101" s="3">
-        <v>16200</v>
+        <v>16600</v>
       </c>
       <c r="I101" s="3">
-        <v>14000</v>
+        <v>14400</v>
       </c>
       <c r="J101" s="3">
-        <v>-20500</v>
+        <v>-21000</v>
       </c>
       <c r="K101" s="3">
         <v>-26000</v>
@@ -4499,25 +4499,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-76700</v>
+        <v>-78600</v>
       </c>
       <c r="E102" s="3">
-        <v>1256900</v>
+        <v>1288100</v>
       </c>
       <c r="F102" s="3">
-        <v>1135800</v>
+        <v>1164100</v>
       </c>
       <c r="G102" s="3">
-        <v>1688100</v>
+        <v>1730100</v>
       </c>
       <c r="H102" s="3">
-        <v>-2175400</v>
+        <v>-2229600</v>
       </c>
       <c r="I102" s="3">
-        <v>1369200</v>
+        <v>1403300</v>
       </c>
       <c r="J102" s="3">
-        <v>-667900</v>
+        <v>-684500</v>
       </c>
       <c r="K102" s="3">
         <v>2213400</v>

--- a/AAII_Financials/Yearly/RWEOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RWEOY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="92">
   <si>
     <t>RWEOY</t>
   </si>
@@ -728,25 +728,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>31639700</v>
+        <v>31575100</v>
       </c>
       <c r="E8" s="3">
-        <v>42494200</v>
+        <v>41054800</v>
       </c>
       <c r="F8" s="3">
-        <v>27214800</v>
+        <v>27943800</v>
       </c>
       <c r="G8" s="3">
-        <v>15160800</v>
+        <v>16858700</v>
       </c>
       <c r="H8" s="3">
-        <v>14537300</v>
+        <v>14837800</v>
       </c>
       <c r="I8" s="3">
-        <v>14848500</v>
+        <v>15400700</v>
       </c>
       <c r="J8" s="3">
-        <v>15309200</v>
+        <v>16658300</v>
       </c>
       <c r="K8" s="3">
         <v>47295200</v>
@@ -773,25 +773,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>22135400</v>
+        <v>22823000</v>
       </c>
       <c r="E9" s="3">
-        <v>34614700</v>
+        <v>33943600</v>
       </c>
       <c r="F9" s="3">
-        <v>19594600</v>
+        <v>20807500</v>
       </c>
       <c r="G9" s="3">
-        <v>10765900</v>
+        <v>12615300</v>
       </c>
       <c r="H9" s="3">
-        <v>9947400</v>
+        <v>10754100</v>
       </c>
       <c r="I9" s="3">
-        <v>11023900</v>
+        <v>11979600</v>
       </c>
       <c r="J9" s="3">
-        <v>11039400</v>
+        <v>12642900</v>
       </c>
       <c r="K9" s="3">
         <v>35950400</v>
@@ -818,25 +818,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>9504300</v>
+        <v>8752100</v>
       </c>
       <c r="E10" s="3">
-        <v>7879500</v>
+        <v>7111300</v>
       </c>
       <c r="F10" s="3">
-        <v>7620300</v>
+        <v>7136400</v>
       </c>
       <c r="G10" s="3">
-        <v>4395000</v>
+        <v>4243400</v>
       </c>
       <c r="H10" s="3">
-        <v>4589900</v>
+        <v>4083700</v>
       </c>
       <c r="I10" s="3">
-        <v>3824500</v>
+        <v>3421100</v>
       </c>
       <c r="J10" s="3">
-        <v>4269800</v>
+        <v>4015400</v>
       </c>
       <c r="K10" s="3">
         <v>11344800</v>
@@ -881,26 +881,26 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E12" s="3">
+        <v>23500</v>
+      </c>
+      <c r="F12" s="3">
+        <v>27300</v>
+      </c>
+      <c r="G12" s="3">
+        <v>26900</v>
+      </c>
+      <c r="H12" s="3">
+        <v>32500</v>
+      </c>
+      <c r="I12" s="3">
+        <v>166000</v>
+      </c>
+      <c r="J12" s="3">
+        <v>343400</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -972,25 +972,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1634800</v>
+        <v>1731000</v>
       </c>
       <c r="E14" s="3">
-        <v>-2059000</v>
+        <v>-1961100</v>
       </c>
       <c r="F14" s="3">
-        <v>605900</v>
+        <v>562900</v>
       </c>
       <c r="G14" s="3">
-        <v>1789900</v>
+        <v>1958400</v>
       </c>
       <c r="H14" s="3">
-        <v>1624800</v>
+        <v>-1325300</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>26300</v>
       </c>
       <c r="J14" s="3">
-        <v>432000</v>
+        <v>-1678700</v>
       </c>
       <c r="K14" s="3">
         <v>4495200</v>
@@ -1017,25 +1017,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2106700</v>
+        <v>2102400</v>
       </c>
       <c r="E15" s="3">
-        <v>1805400</v>
+        <v>1742000</v>
       </c>
       <c r="F15" s="3">
-        <v>1573900</v>
+        <v>1616100</v>
       </c>
       <c r="G15" s="3">
-        <v>1577200</v>
+        <v>1741900</v>
       </c>
       <c r="H15" s="3">
-        <v>1326900</v>
+        <v>1344400</v>
       </c>
       <c r="I15" s="3">
-        <v>997900</v>
+        <v>1031600</v>
       </c>
       <c r="J15" s="3">
-        <v>1054400</v>
+        <v>563200</v>
       </c>
       <c r="K15" s="3">
         <v>2459700</v>
@@ -1078,25 +1078,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>27301200</v>
+        <v>25397400</v>
       </c>
       <c r="E17" s="3">
-        <v>42912900</v>
+        <v>43172000</v>
       </c>
       <c r="F17" s="3">
-        <v>25981000</v>
+        <v>26083200</v>
       </c>
       <c r="G17" s="3">
-        <v>13610200</v>
+        <v>13382300</v>
       </c>
       <c r="H17" s="3">
-        <v>14695600</v>
+        <v>16362900</v>
       </c>
       <c r="I17" s="3">
-        <v>14528400</v>
+        <v>15147700</v>
       </c>
       <c r="J17" s="3">
-        <v>13136100</v>
+        <v>16278800</v>
       </c>
       <c r="K17" s="3">
         <v>51764300</v>
@@ -1123,25 +1123,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>4338500</v>
+        <v>6177700</v>
       </c>
       <c r="E18" s="3">
-        <v>-418700</v>
+        <v>-2117100</v>
       </c>
       <c r="F18" s="3">
-        <v>1233900</v>
+        <v>1860600</v>
       </c>
       <c r="G18" s="3">
-        <v>1550600</v>
+        <v>3476500</v>
       </c>
       <c r="H18" s="3">
-        <v>-158400</v>
+        <v>-1525100</v>
       </c>
       <c r="I18" s="3">
-        <v>320100</v>
+        <v>253000</v>
       </c>
       <c r="J18" s="3">
-        <v>2173100</v>
+        <v>379400</v>
       </c>
       <c r="K18" s="3">
         <v>-4469100</v>
@@ -1187,25 +1187,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1218400</v>
+        <v>-547100</v>
       </c>
       <c r="E20" s="3">
-        <v>2114400</v>
+        <v>-1362600</v>
       </c>
       <c r="F20" s="3">
-        <v>828500</v>
+        <v>-439000</v>
       </c>
       <c r="G20" s="3">
-        <v>178300</v>
+        <v>-237300</v>
       </c>
       <c r="H20" s="3">
-        <v>-388800</v>
+        <v>-318700</v>
       </c>
       <c r="I20" s="3">
-        <v>-66500</v>
+        <v>-85900</v>
       </c>
       <c r="J20" s="3">
-        <v>434200</v>
+        <v>-401100</v>
       </c>
       <c r="K20" s="3">
         <v>-839800</v>
@@ -1232,25 +1232,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>9788200</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>8</v>
+        <v>8827200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>987500</v>
       </c>
       <c r="F21" s="3">
-        <v>4406700</v>
+        <v>3915600</v>
       </c>
       <c r="G21" s="3">
-        <v>5249400</v>
+        <v>5455700</v>
       </c>
       <c r="H21" s="3">
-        <v>2502600</v>
+        <v>138000</v>
       </c>
       <c r="I21" s="3">
-        <v>1314500</v>
+        <v>1370500</v>
       </c>
       <c r="J21" s="3">
-        <v>3679300</v>
+        <v>1343700</v>
       </c>
       <c r="K21" s="3">
         <v>1925400</v>
@@ -1277,25 +1277,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1119800</v>
+        <v>1492200</v>
       </c>
       <c r="E22" s="3">
-        <v>903800</v>
+        <v>822900</v>
       </c>
       <c r="F22" s="3">
-        <v>376600</v>
+        <v>449200</v>
       </c>
       <c r="G22" s="3">
-        <v>327800</v>
+        <v>554100</v>
       </c>
       <c r="H22" s="3">
-        <v>285800</v>
+        <v>1179400</v>
       </c>
       <c r="I22" s="3">
-        <v>199400</v>
+        <v>446500</v>
       </c>
       <c r="J22" s="3">
-        <v>330100</v>
+        <v>559600</v>
       </c>
       <c r="K22" s="3">
         <v>991700</v>
@@ -1322,25 +1322,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>4437000</v>
+        <v>4428000</v>
       </c>
       <c r="E23" s="3">
-        <v>791900</v>
+        <v>764100</v>
       </c>
       <c r="F23" s="3">
-        <v>1685800</v>
+        <v>1730900</v>
       </c>
       <c r="G23" s="3">
-        <v>1401100</v>
+        <v>1547400</v>
       </c>
       <c r="H23" s="3">
-        <v>-832900</v>
+        <v>-843900</v>
       </c>
       <c r="I23" s="3">
-        <v>54300</v>
+        <v>56100</v>
       </c>
       <c r="J23" s="3">
-        <v>2277200</v>
+        <v>2468800</v>
       </c>
       <c r="K23" s="3">
         <v>-6300600</v>
@@ -1367,25 +1367,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>2668200</v>
+        <v>2662800</v>
       </c>
       <c r="E24" s="3">
-        <v>-2522000</v>
+        <v>-2433500</v>
       </c>
       <c r="F24" s="3">
-        <v>764200</v>
+        <v>784700</v>
       </c>
       <c r="G24" s="3">
-        <v>416500</v>
+        <v>459900</v>
       </c>
       <c r="H24" s="3">
-        <v>-101900</v>
+        <v>-103200</v>
       </c>
       <c r="I24" s="3">
-        <v>114100</v>
+        <v>117900</v>
       </c>
       <c r="J24" s="3">
-        <v>368800</v>
+        <v>399900</v>
       </c>
       <c r="K24" s="3">
         <v>-350500</v>
@@ -1457,25 +1457,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1768800</v>
+        <v>1765200</v>
       </c>
       <c r="E26" s="3">
-        <v>3313900</v>
+        <v>3197600</v>
       </c>
       <c r="F26" s="3">
-        <v>921500</v>
+        <v>946200</v>
       </c>
       <c r="G26" s="3">
-        <v>984700</v>
+        <v>1087500</v>
       </c>
       <c r="H26" s="3">
-        <v>-731000</v>
+        <v>-740700</v>
       </c>
       <c r="I26" s="3">
-        <v>-59800</v>
+        <v>-61800</v>
       </c>
       <c r="J26" s="3">
-        <v>1908400</v>
+        <v>2068900</v>
       </c>
       <c r="K26" s="3">
         <v>-5950100</v>
@@ -1502,25 +1502,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1606000</v>
+        <v>1602700</v>
       </c>
       <c r="E27" s="3">
-        <v>3009300</v>
+        <v>2903700</v>
       </c>
       <c r="F27" s="3">
-        <v>798600</v>
+        <v>820000</v>
       </c>
       <c r="G27" s="3">
-        <v>919300</v>
+        <v>1285600</v>
       </c>
       <c r="H27" s="3">
-        <v>-1459800</v>
+        <v>9536500</v>
       </c>
       <c r="I27" s="3">
-        <v>-877200</v>
+        <v>383600</v>
       </c>
       <c r="J27" s="3">
-        <v>1448700</v>
+        <v>2281500</v>
       </c>
       <c r="K27" s="3">
         <v>-6195400</v>
@@ -1591,26 +1591,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>244800</v>
+        <v>270300</v>
       </c>
       <c r="H29" s="3">
-        <v>10872200</v>
+        <v>11015600</v>
       </c>
       <c r="I29" s="3">
-        <v>1248300</v>
+        <v>1290400</v>
       </c>
       <c r="J29" s="3">
-        <v>655700</v>
+        <v>710900</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1727,25 +1727,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1218400</v>
+        <v>547100</v>
       </c>
       <c r="E32" s="3">
-        <v>-2114400</v>
+        <v>1362600</v>
       </c>
       <c r="F32" s="3">
-        <v>-828500</v>
+        <v>439000</v>
       </c>
       <c r="G32" s="3">
-        <v>-178300</v>
+        <v>237300</v>
       </c>
       <c r="H32" s="3">
-        <v>388800</v>
+        <v>318700</v>
       </c>
       <c r="I32" s="3">
-        <v>66500</v>
+        <v>85900</v>
       </c>
       <c r="J32" s="3">
-        <v>-434200</v>
+        <v>401100</v>
       </c>
       <c r="K32" s="3">
         <v>839800</v>
@@ -1772,25 +1772,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1606000</v>
+        <v>1602700</v>
       </c>
       <c r="E33" s="3">
-        <v>3009300</v>
+        <v>2903700</v>
       </c>
       <c r="F33" s="3">
-        <v>798600</v>
+        <v>820000</v>
       </c>
       <c r="G33" s="3">
-        <v>1164100</v>
+        <v>1285600</v>
       </c>
       <c r="H33" s="3">
-        <v>9412400</v>
+        <v>9553400</v>
       </c>
       <c r="I33" s="3">
-        <v>371000</v>
+        <v>451100</v>
       </c>
       <c r="J33" s="3">
-        <v>2104400</v>
+        <v>2331900</v>
       </c>
       <c r="K33" s="3">
         <v>-6195400</v>
@@ -1862,25 +1862,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1606000</v>
+        <v>1602700</v>
       </c>
       <c r="E35" s="3">
-        <v>3009300</v>
+        <v>2903700</v>
       </c>
       <c r="F35" s="3">
-        <v>798600</v>
+        <v>820000</v>
       </c>
       <c r="G35" s="3">
-        <v>1164100</v>
+        <v>1285600</v>
       </c>
       <c r="H35" s="3">
-        <v>9412400</v>
+        <v>9553400</v>
       </c>
       <c r="I35" s="3">
-        <v>371000</v>
+        <v>451100</v>
       </c>
       <c r="J35" s="3">
-        <v>2104400</v>
+        <v>2331900</v>
       </c>
       <c r="K35" s="3">
         <v>-6195400</v>
@@ -1995,25 +1995,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>7661300</v>
+        <v>7645600</v>
       </c>
       <c r="E41" s="3">
-        <v>7739900</v>
+        <v>7468200</v>
       </c>
       <c r="F41" s="3">
-        <v>6451800</v>
+        <v>6624600</v>
       </c>
       <c r="G41" s="3">
-        <v>5287700</v>
+        <v>5839800</v>
       </c>
       <c r="H41" s="3">
-        <v>7070900</v>
+        <v>3582100</v>
       </c>
       <c r="I41" s="3">
-        <v>3902100</v>
+        <v>4033700</v>
       </c>
       <c r="J41" s="3">
-        <v>4356200</v>
+        <v>4722600</v>
       </c>
       <c r="K41" s="3">
         <v>4965000</v>
@@ -2040,25 +2040,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>8555100</v>
+        <v>8537600</v>
       </c>
       <c r="E42" s="3">
-        <v>14917200</v>
+        <v>14393500</v>
       </c>
       <c r="F42" s="3">
-        <v>8905100</v>
+        <v>9143600</v>
       </c>
       <c r="G42" s="3">
-        <v>4673000</v>
+        <v>5160900</v>
       </c>
       <c r="H42" s="3">
-        <v>3608600</v>
+        <v>3656200</v>
       </c>
       <c r="I42" s="3">
-        <v>3997300</v>
+        <v>4132100</v>
       </c>
       <c r="J42" s="3">
-        <v>5419500</v>
+        <v>5875400</v>
       </c>
       <c r="K42" s="3">
         <v>10660100</v>
@@ -2085,25 +2085,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>20198200</v>
+        <v>9365500</v>
       </c>
       <c r="E43" s="3">
-        <v>20684400</v>
+        <v>11253600</v>
       </c>
       <c r="F43" s="3">
-        <v>21366700</v>
+        <v>8295200</v>
       </c>
       <c r="G43" s="3">
-        <v>9662700</v>
+        <v>4358400</v>
       </c>
       <c r="H43" s="3">
-        <v>10851200</v>
+        <v>5092600</v>
       </c>
       <c r="I43" s="3">
-        <v>5367400</v>
+        <v>2734100</v>
       </c>
       <c r="J43" s="3">
-        <v>8412200</v>
+        <v>7857800</v>
       </c>
       <c r="K43" s="3">
         <v>7273800</v>
@@ -2130,25 +2130,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>5028500</v>
+        <v>2509100</v>
       </c>
       <c r="E44" s="3">
-        <v>4658600</v>
+        <v>4495000</v>
       </c>
       <c r="F44" s="3">
-        <v>3132300</v>
+        <v>3216200</v>
       </c>
       <c r="G44" s="3">
-        <v>3615200</v>
+        <v>1996300</v>
       </c>
       <c r="H44" s="3">
-        <v>3511100</v>
+        <v>1778700</v>
       </c>
       <c r="I44" s="3">
-        <v>1806500</v>
+        <v>1867400</v>
       </c>
       <c r="J44" s="3">
-        <v>2131000</v>
+        <v>2310300</v>
       </c>
       <c r="K44" s="3">
         <v>2135300</v>
@@ -2175,25 +2175,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>61968000</v>
+        <v>31329700</v>
       </c>
       <c r="E45" s="3">
-        <v>58619700</v>
+        <v>65046500</v>
       </c>
       <c r="F45" s="3">
-        <v>74720900</v>
+        <v>90176300</v>
       </c>
       <c r="G45" s="3">
-        <v>25932200</v>
+        <v>15765100</v>
       </c>
       <c r="H45" s="3">
-        <v>32498100</v>
+        <v>17421200</v>
       </c>
       <c r="I45" s="3">
-        <v>53058500</v>
+        <v>57505200</v>
       </c>
       <c r="J45" s="3">
-        <v>5560200</v>
+        <v>7029300</v>
       </c>
       <c r="K45" s="3">
         <v>8048500</v>
@@ -2220,25 +2220,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>59825900</v>
+        <v>59679500</v>
       </c>
       <c r="E46" s="3">
-        <v>106620000</v>
+        <v>102877000</v>
       </c>
       <c r="F46" s="3">
-        <v>114577000</v>
+        <v>117645900</v>
       </c>
       <c r="G46" s="3">
-        <v>30153300</v>
+        <v>33301500</v>
       </c>
       <c r="H46" s="3">
-        <v>31279700</v>
+        <v>31692300</v>
       </c>
       <c r="I46" s="3">
-        <v>68131800</v>
+        <v>70429400</v>
       </c>
       <c r="J46" s="3">
-        <v>25879100</v>
+        <v>28056000</v>
       </c>
       <c r="K46" s="3">
         <v>33082700</v>
@@ -2265,25 +2265,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>11158000</v>
+        <v>10547100</v>
       </c>
       <c r="E47" s="3">
-        <v>9327100</v>
+        <v>8699400</v>
       </c>
       <c r="F47" s="3">
-        <v>9793400</v>
+        <v>9495100</v>
       </c>
       <c r="G47" s="3">
-        <v>8623800</v>
+        <v>9149800</v>
       </c>
       <c r="H47" s="3">
-        <v>8871900</v>
+        <v>8512000</v>
       </c>
       <c r="I47" s="3">
-        <v>2462200</v>
+        <v>2097500</v>
       </c>
       <c r="J47" s="3">
-        <v>5039600</v>
+        <v>4630200</v>
       </c>
       <c r="K47" s="3">
         <v>4974700</v>
@@ -2310,25 +2310,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>63816600</v>
+        <v>24425800</v>
       </c>
       <c r="E48" s="3">
-        <v>26304400</v>
+        <v>21058000</v>
       </c>
       <c r="F48" s="3">
-        <v>22134300</v>
+        <v>19174300</v>
       </c>
       <c r="G48" s="3">
-        <v>39657600</v>
+        <v>17105800</v>
       </c>
       <c r="H48" s="3">
-        <v>42066600</v>
+        <v>17579400</v>
       </c>
       <c r="I48" s="3">
-        <v>13744200</v>
+        <v>12737600</v>
       </c>
       <c r="J48" s="3">
-        <v>27631300</v>
+        <v>28195200</v>
       </c>
       <c r="K48" s="3">
         <v>26602000</v>
@@ -2355,25 +2355,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>21654700</v>
+        <v>10791400</v>
       </c>
       <c r="E49" s="3">
-        <v>6259000</v>
+        <v>6038300</v>
       </c>
       <c r="F49" s="3">
-        <v>6486100</v>
+        <v>6656400</v>
       </c>
       <c r="G49" s="3">
-        <v>10856700</v>
+        <v>5976800</v>
       </c>
       <c r="H49" s="3">
-        <v>10669500</v>
+        <v>5349600</v>
       </c>
       <c r="I49" s="3">
-        <v>2419000</v>
+        <v>2497100</v>
       </c>
       <c r="J49" s="3">
-        <v>13681100</v>
+        <v>14414000</v>
       </c>
       <c r="K49" s="3">
         <v>13826200</v>
@@ -2490,25 +2490,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>8281500</v>
+        <v>11430300</v>
       </c>
       <c r="E52" s="3">
-        <v>4945400</v>
+        <v>8596800</v>
       </c>
       <c r="F52" s="3">
-        <v>4630900</v>
+        <v>7999500</v>
       </c>
       <c r="G52" s="3">
-        <v>8360200</v>
+        <v>9251400</v>
       </c>
       <c r="H52" s="3">
-        <v>8462100</v>
+        <v>7805000</v>
       </c>
       <c r="I52" s="3">
-        <v>1970400</v>
+        <v>2917300</v>
       </c>
       <c r="J52" s="3">
-        <v>4258700</v>
+        <v>3771600</v>
       </c>
       <c r="K52" s="3">
         <v>4410500</v>
@@ -2580,25 +2580,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>117973000</v>
+        <v>117711900</v>
       </c>
       <c r="E54" s="3">
-        <v>153456000</v>
+        <v>148068800</v>
       </c>
       <c r="F54" s="3">
-        <v>157621000</v>
+        <v>161843500</v>
       </c>
       <c r="G54" s="3">
-        <v>68274700</v>
+        <v>75403100</v>
       </c>
       <c r="H54" s="3">
-        <v>70896400</v>
+        <v>71831400</v>
       </c>
       <c r="I54" s="3">
-        <v>88727600</v>
+        <v>91719700</v>
       </c>
       <c r="J54" s="3">
-        <v>76489700</v>
+        <v>82923900</v>
       </c>
       <c r="K54" s="3">
         <v>82896200</v>
@@ -2663,25 +2663,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>5664300</v>
+        <v>5652700</v>
       </c>
       <c r="E57" s="3">
-        <v>8267100</v>
+        <v>7976900</v>
       </c>
       <c r="F57" s="3">
-        <v>4904500</v>
+        <v>5035800</v>
       </c>
       <c r="G57" s="3">
-        <v>2643800</v>
+        <v>2919900</v>
       </c>
       <c r="H57" s="3">
-        <v>3308400</v>
+        <v>3352000</v>
       </c>
       <c r="I57" s="3">
-        <v>2690400</v>
+        <v>2781100</v>
       </c>
       <c r="J57" s="3">
-        <v>5623300</v>
+        <v>6096300</v>
       </c>
       <c r="K57" s="3">
         <v>5892600</v>
@@ -2708,25 +2708,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4496900</v>
+        <v>3276200</v>
       </c>
       <c r="E58" s="3">
-        <v>9609500</v>
+        <v>11984600</v>
       </c>
       <c r="F58" s="3">
-        <v>7049900</v>
+        <v>12505400</v>
       </c>
       <c r="G58" s="3">
-        <v>1568400</v>
+        <v>1525400</v>
       </c>
       <c r="H58" s="3">
-        <v>2395700</v>
+        <v>1895400</v>
       </c>
       <c r="I58" s="3">
-        <v>100800</v>
+        <v>877000</v>
       </c>
       <c r="J58" s="3">
-        <v>1902900</v>
+        <v>3346500</v>
       </c>
       <c r="K58" s="3">
         <v>958100</v>
@@ -2753,25 +2753,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>52539000</v>
+        <v>27587000</v>
       </c>
       <c r="E59" s="3">
-        <v>70382400</v>
+        <v>63773600</v>
       </c>
       <c r="F59" s="3">
-        <v>95490600</v>
+        <v>91554600</v>
       </c>
       <c r="G59" s="3">
-        <v>25726200</v>
+        <v>14730300</v>
       </c>
       <c r="H59" s="3">
-        <v>32502500</v>
+        <v>15889400</v>
       </c>
       <c r="I59" s="3">
-        <v>47985700</v>
+        <v>48174900</v>
       </c>
       <c r="J59" s="3">
-        <v>14951500</v>
+        <v>12484400</v>
       </c>
       <c r="K59" s="3">
         <v>24360400</v>
@@ -2798,25 +2798,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>37956300</v>
+        <v>37878900</v>
       </c>
       <c r="E60" s="3">
-        <v>88259100</v>
+        <v>85160800</v>
       </c>
       <c r="F60" s="3">
-        <v>107445000</v>
+        <v>110323000</v>
       </c>
       <c r="G60" s="3">
-        <v>18276500</v>
+        <v>20184700</v>
       </c>
       <c r="H60" s="3">
-        <v>21714500</v>
+        <v>22000900</v>
       </c>
       <c r="I60" s="3">
-        <v>50776800</v>
+        <v>52489100</v>
       </c>
       <c r="J60" s="3">
-        <v>22477600</v>
+        <v>24368400</v>
       </c>
       <c r="K60" s="3">
         <v>31211100</v>
@@ -2843,25 +2843,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>15577300</v>
+        <v>15545500</v>
       </c>
       <c r="E61" s="3">
-        <v>9452300</v>
+        <v>10461700</v>
       </c>
       <c r="F61" s="3">
-        <v>6378700</v>
+        <v>7731100</v>
       </c>
       <c r="G61" s="3">
-        <v>3651800</v>
+        <v>4833000</v>
       </c>
       <c r="H61" s="3">
-        <v>3436900</v>
+        <v>4403500</v>
       </c>
       <c r="I61" s="3">
-        <v>2001400</v>
+        <v>2287600</v>
       </c>
       <c r="J61" s="3">
-        <v>15095500</v>
+        <v>17307900</v>
       </c>
       <c r="K61" s="3">
         <v>16589600</v>
@@ -2888,25 +2888,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>51108000</v>
+        <v>20235400</v>
       </c>
       <c r="E62" s="3">
-        <v>23315000</v>
+        <v>18290100</v>
       </c>
       <c r="F62" s="3">
-        <v>24973100</v>
+        <v>20045500</v>
       </c>
       <c r="G62" s="3">
-        <v>50683800</v>
+        <v>21722300</v>
       </c>
       <c r="H62" s="3">
-        <v>51538800</v>
+        <v>19529800</v>
       </c>
       <c r="I62" s="3">
-        <v>20158300</v>
+        <v>14980500</v>
       </c>
       <c r="J62" s="3">
-        <v>25635400</v>
+        <v>19478900</v>
       </c>
       <c r="K62" s="3">
         <v>26426300</v>
@@ -3068,25 +3068,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>82986900</v>
+        <v>81081000</v>
       </c>
       <c r="E66" s="3">
-        <v>122913000</v>
+        <v>116777800</v>
       </c>
       <c r="F66" s="3">
-        <v>140726000</v>
+        <v>142514500</v>
       </c>
       <c r="G66" s="3">
-        <v>49538500</v>
+        <v>53744300</v>
       </c>
       <c r="H66" s="3">
-        <v>52107000</v>
+        <v>52229800</v>
       </c>
       <c r="I66" s="3">
-        <v>79051600</v>
+        <v>75396200</v>
       </c>
       <c r="J66" s="3">
-        <v>69003500</v>
+        <v>68525500</v>
       </c>
       <c r="K66" s="3">
         <v>79908100</v>
@@ -3312,25 +3312,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>15963800</v>
+        <v>15931200</v>
       </c>
       <c r="E72" s="3">
-        <v>17425900</v>
+        <v>16814100</v>
       </c>
       <c r="F72" s="3">
-        <v>11856900</v>
+        <v>12174500</v>
       </c>
       <c r="G72" s="3">
-        <v>9196400</v>
+        <v>10156600</v>
       </c>
       <c r="H72" s="3">
-        <v>9866500</v>
+        <v>9996600</v>
       </c>
       <c r="I72" s="3">
-        <v>1261600</v>
+        <v>1304100</v>
       </c>
       <c r="J72" s="3">
-        <v>2621700</v>
+        <v>2842200</v>
       </c>
       <c r="K72" s="3">
         <v>-707400</v>
@@ -3492,25 +3492,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>34985800</v>
+        <v>34894400</v>
       </c>
       <c r="E76" s="3">
-        <v>30543200</v>
+        <v>29471000</v>
       </c>
       <c r="F76" s="3">
-        <v>16895300</v>
+        <v>17347900</v>
       </c>
       <c r="G76" s="3">
-        <v>18736200</v>
+        <v>20692400</v>
       </c>
       <c r="H76" s="3">
-        <v>18789300</v>
+        <v>19037100</v>
       </c>
       <c r="I76" s="3">
-        <v>9676000</v>
+        <v>11078500</v>
       </c>
       <c r="J76" s="3">
-        <v>7486300</v>
+        <v>9244700</v>
       </c>
       <c r="K76" s="3">
         <v>2988100</v>
@@ -3632,25 +3632,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1606000</v>
+        <v>1602700</v>
       </c>
       <c r="E81" s="3">
-        <v>3009300</v>
+        <v>2903700</v>
       </c>
       <c r="F81" s="3">
-        <v>798600</v>
+        <v>820000</v>
       </c>
       <c r="G81" s="3">
-        <v>1164100</v>
+        <v>1285600</v>
       </c>
       <c r="H81" s="3">
-        <v>9412400</v>
+        <v>9553400</v>
       </c>
       <c r="I81" s="3">
-        <v>371000</v>
+        <v>451100</v>
       </c>
       <c r="J81" s="3">
-        <v>2104400</v>
+        <v>2331900</v>
       </c>
       <c r="K81" s="3">
         <v>-6195400</v>
@@ -3696,25 +3696,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>4232100</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>8</v>
+        <v>1763000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>1532500</v>
       </c>
       <c r="F83" s="3">
-        <v>2344800</v>
+        <v>1415900</v>
       </c>
       <c r="G83" s="3">
-        <v>3521100</v>
+        <v>1603700</v>
       </c>
       <c r="H83" s="3">
-        <v>3050300</v>
+        <v>813600</v>
       </c>
       <c r="I83" s="3">
-        <v>1061100</v>
+        <v>922800</v>
       </c>
       <c r="J83" s="3">
-        <v>1072200</v>
+        <v>-146500</v>
       </c>
       <c r="K83" s="3">
         <v>7237000</v>
@@ -3966,25 +3966,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>4690700</v>
+        <v>4681100</v>
       </c>
       <c r="E89" s="3">
-        <v>2664900</v>
+        <v>2571300</v>
       </c>
       <c r="F89" s="3">
-        <v>8056700</v>
+        <v>8272500</v>
       </c>
       <c r="G89" s="3">
-        <v>4624200</v>
+        <v>5107000</v>
       </c>
       <c r="H89" s="3">
-        <v>-1686900</v>
+        <v>-1709100</v>
       </c>
       <c r="I89" s="3">
-        <v>7363300</v>
+        <v>7611600</v>
       </c>
       <c r="J89" s="3">
-        <v>-1942700</v>
+        <v>-2106100</v>
       </c>
       <c r="K89" s="3">
         <v>2551900</v>
@@ -4030,25 +4030,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-11052700</v>
+        <v>-11030200</v>
       </c>
       <c r="E91" s="3">
-        <v>-4966500</v>
+        <v>-4792100</v>
       </c>
       <c r="F91" s="3">
-        <v>-4174500</v>
+        <v>-4286400</v>
       </c>
       <c r="G91" s="3">
-        <v>-3719300</v>
+        <v>-4107600</v>
       </c>
       <c r="H91" s="3">
-        <v>-1961600</v>
+        <v>-1987400</v>
       </c>
       <c r="I91" s="3">
-        <v>-1380100</v>
+        <v>-1426600</v>
       </c>
       <c r="J91" s="3">
-        <v>-3474500</v>
+        <v>-1083100</v>
       </c>
       <c r="K91" s="3">
         <v>-2504200</v>
@@ -4165,25 +4165,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-3112400</v>
+        <v>-3106000</v>
       </c>
       <c r="E94" s="3">
-        <v>-10956400</v>
+        <v>-10571800</v>
       </c>
       <c r="F94" s="3">
-        <v>-8570600</v>
+        <v>-8800200</v>
       </c>
       <c r="G94" s="3">
-        <v>-4822500</v>
+        <v>-5326000</v>
       </c>
       <c r="H94" s="3">
-        <v>-807400</v>
+        <v>-818100</v>
       </c>
       <c r="I94" s="3">
-        <v>-4877900</v>
+        <v>-5042400</v>
       </c>
       <c r="J94" s="3">
-        <v>2980600</v>
+        <v>3231300</v>
       </c>
       <c r="K94" s="3">
         <v>-4958500</v>
@@ -4229,25 +4229,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1044500</v>
+        <v>739500</v>
       </c>
       <c r="E96" s="3">
-        <v>-1011200</v>
+        <v>650800</v>
       </c>
       <c r="F96" s="3">
-        <v>-808500</v>
+        <v>653900</v>
       </c>
       <c r="G96" s="3">
-        <v>-578200</v>
+        <v>638500</v>
       </c>
       <c r="H96" s="3">
-        <v>-620300</v>
+        <v>628400</v>
       </c>
       <c r="I96" s="3">
-        <v>-1135300</v>
+        <v>1173600</v>
       </c>
       <c r="J96" s="3">
-        <v>-176100</v>
+        <v>190900</v>
       </c>
       <c r="K96" s="3">
         <v>-441600</v>
@@ -4409,25 +4409,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1724500</v>
+        <v>-1721000</v>
       </c>
       <c r="E100" s="3">
-        <v>9542000</v>
+        <v>9207000</v>
       </c>
       <c r="F100" s="3">
-        <v>1613800</v>
+        <v>1657000</v>
       </c>
       <c r="G100" s="3">
-        <v>1966000</v>
+        <v>2171300</v>
       </c>
       <c r="H100" s="3">
-        <v>248100</v>
+        <v>251400</v>
       </c>
       <c r="I100" s="3">
-        <v>-1096500</v>
+        <v>-1133500</v>
       </c>
       <c r="J100" s="3">
-        <v>-1701300</v>
+        <v>-1844400</v>
       </c>
       <c r="K100" s="3">
         <v>4646000</v>
@@ -4454,25 +4454,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>67600</v>
+        <v>67400</v>
       </c>
       <c r="E101" s="3">
-        <v>37700</v>
+        <v>36300</v>
       </c>
       <c r="F101" s="3">
-        <v>64200</v>
+        <v>66000</v>
       </c>
       <c r="G101" s="3">
-        <v>-37700</v>
+        <v>-41600</v>
       </c>
       <c r="H101" s="3">
-        <v>16600</v>
+        <v>16800</v>
       </c>
       <c r="I101" s="3">
-        <v>14400</v>
+        <v>14900</v>
       </c>
       <c r="J101" s="3">
-        <v>-21000</v>
+        <v>-22800</v>
       </c>
       <c r="K101" s="3">
         <v>-26000</v>
@@ -4499,25 +4499,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-78600</v>
+        <v>-78500</v>
       </c>
       <c r="E102" s="3">
-        <v>1288100</v>
+        <v>1242900</v>
       </c>
       <c r="F102" s="3">
-        <v>1164100</v>
+        <v>1195300</v>
       </c>
       <c r="G102" s="3">
-        <v>1730100</v>
+        <v>1910700</v>
       </c>
       <c r="H102" s="3">
-        <v>-2229600</v>
+        <v>-2259000</v>
       </c>
       <c r="I102" s="3">
-        <v>1403300</v>
+        <v>1450700</v>
       </c>
       <c r="J102" s="3">
-        <v>-684500</v>
+        <v>-742100</v>
       </c>
       <c r="K102" s="3">
         <v>2213400</v>

--- a/AAII_Financials/Yearly/RWEOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RWEOY_YR_FIN.xlsx
@@ -4030,13 +4030,13 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-11030200</v>
+        <v>-5688100</v>
       </c>
       <c r="E91" s="3">
-        <v>-4792100</v>
+        <v>-3530000</v>
       </c>
       <c r="F91" s="3">
-        <v>-4286400</v>
+        <v>-4195400</v>
       </c>
       <c r="G91" s="3">
         <v>-4107600</v>

--- a/AAII_Financials/Yearly/RWEOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RWEOY_YR_FIN.xlsx
@@ -656,209 +656,221 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>31575100</v>
+        <v>25079200</v>
       </c>
       <c r="E8" s="3">
+        <v>31525400</v>
+      </c>
+      <c r="F8" s="3">
         <v>41054800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>27943800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>16858700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>14837800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>15400700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>16658300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>47295200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>48507200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>50344400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>59509800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>55746600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>57696300</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>22823000</v>
+        <v>16498600</v>
       </c>
       <c r="E9" s="3">
+        <v>19512500</v>
+      </c>
+      <c r="F9" s="3">
         <v>33943600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>20807500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>12615300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10754100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>11979600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12642900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>35950400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>35441900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>36444000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>42205500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>37643800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>39455300</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>8752100</v>
+        <v>8580600</v>
       </c>
       <c r="E10" s="3">
+        <v>12012800</v>
+      </c>
+      <c r="F10" s="3">
         <v>7111300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7136400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4243400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4083700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3421100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4015400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>11344800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>13065200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>13900400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>17304200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>18102700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>18241000</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -876,34 +888,35 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E12" s="3">
         <v>19900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>23500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>27300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>26900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>32500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>166000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>343400</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
@@ -920,9 +933,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -965,99 +981,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1731000</v>
+        <v>974200</v>
       </c>
       <c r="E14" s="3">
+        <v>1760800</v>
+      </c>
+      <c r="F14" s="3">
         <v>-1961100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>562900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1958400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-1325300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>26300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-1678700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4495200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2880900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>593500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>5705900</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2102400</v>
+        <v>1941200</v>
       </c>
       <c r="E15" s="3">
+        <v>2101200</v>
+      </c>
+      <c r="F15" s="3">
         <v>1742000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1616100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1741900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1344400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1031600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>563200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2459700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2551900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2478500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2997700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>5568000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>3995600</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1072,98 +1097,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>25397400</v>
+        <v>18048500</v>
       </c>
       <c r="E17" s="3">
+        <v>25366400</v>
+      </c>
+      <c r="F17" s="3">
         <v>43172000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>26083200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13382300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>16362900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15147700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>16278800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>51764300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>48012000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>46471700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>59888900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>51524700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>52849600</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>6177700</v>
+        <v>7030700</v>
       </c>
       <c r="E18" s="3">
+        <v>6158900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2117100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1860600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3476500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1525100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>253000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>379400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4469100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>495100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3872700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-379200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4221800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4846700</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1181,233 +1213,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-547100</v>
+        <v>-597400</v>
       </c>
       <c r="E20" s="3">
-        <v>-1362600</v>
+        <v>-787000</v>
       </c>
       <c r="F20" s="3">
+        <v>-1724900</v>
+      </c>
+      <c r="G20" s="3">
         <v>-439000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-237300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-318700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-85900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-401100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-839800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-38100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-244400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>570600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-401900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-49300</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>8827200</v>
+        <v>9569300</v>
       </c>
       <c r="E21" s="3">
-        <v>987500</v>
+        <v>9047200</v>
       </c>
       <c r="F21" s="3">
+        <v>1349800</v>
+      </c>
+      <c r="G21" s="3">
         <v>3915600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5455700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>138000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1370500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1343700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1925400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6391200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7042800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8901000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>9709900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>8841500</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1492200</v>
+        <v>895500</v>
       </c>
       <c r="E22" s="3">
-        <v>822900</v>
+        <v>1726500</v>
       </c>
       <c r="F22" s="3">
+        <v>1185200</v>
+      </c>
+      <c r="G22" s="3">
         <v>449200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>554100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1179400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>446500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>559600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>991700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1131000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1178200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2602900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1371400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1247800</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>4428000</v>
+        <v>6566900</v>
       </c>
       <c r="E23" s="3">
+        <v>4420200</v>
+      </c>
+      <c r="F23" s="3">
         <v>764100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1730900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1547400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-843900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>56100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2468800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-6300600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-673900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2450200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2411500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2448500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3549600</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>2662800</v>
+        <v>1091200</v>
       </c>
       <c r="E24" s="3">
+        <v>2583200</v>
+      </c>
+      <c r="F24" s="3">
         <v>-2433500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>784700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>459900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-103200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>117900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>399900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-350500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>638000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>603300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>884000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>577500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1002400</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1450,99 +1498,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>1765200</v>
+        <v>5475700</v>
       </c>
       <c r="E26" s="3">
+        <v>1837100</v>
+      </c>
+      <c r="F26" s="3">
         <v>3197600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>946200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1087500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-740700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-61800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2068900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5950100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1311900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1846900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3295500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1871000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2547200</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>1602700</v>
+        <v>5316300</v>
       </c>
       <c r="E27" s="3">
+        <v>1674600</v>
+      </c>
+      <c r="F27" s="3">
         <v>2903700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>820000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1285600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>9536500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>383600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2281500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-6195400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1792300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1461800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3671100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1434000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2119900</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1585,9 +1642,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1601,38 +1661,41 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>270300</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>11015600</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>1290400</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>710900</v>
       </c>
-      <c r="K29" s="3" t="s">
+      <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>1612400</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>397100</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>373200</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1675,9 +1738,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1720,99 +1786,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>547100</v>
+        <v>597400</v>
       </c>
       <c r="E32" s="3">
-        <v>1362600</v>
+        <v>787000</v>
       </c>
       <c r="F32" s="3">
+        <v>1724900</v>
+      </c>
+      <c r="G32" s="3">
         <v>439000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>237300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>318700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>85900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>401100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>839800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>38100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>244400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-570600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>401900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>49300</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>1602700</v>
+        <v>5316300</v>
       </c>
       <c r="E33" s="3">
+        <v>1674600</v>
+      </c>
+      <c r="F33" s="3">
         <v>2903700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>820000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1285600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>9553400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>451100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2331900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-6195400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-179900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1858900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3297900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1434000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2119900</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1855,104 +1930,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>1602700</v>
+        <v>5316300</v>
       </c>
       <c r="E35" s="3">
+        <v>1674600</v>
+      </c>
+      <c r="F35" s="3">
         <v>2903700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>820000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1285600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>9553400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>451100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2331900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-6195400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-179900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1858900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3297900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1434000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2119900</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1970,8 +2054,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1989,413 +2074,441 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5269700</v>
+      </c>
+      <c r="E41" s="3">
         <v>7645600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7468200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6624600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5839800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3582100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4033700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4722600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4965000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2668300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3459300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>9450000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5662400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4307900</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>7092900</v>
+      </c>
+      <c r="E42" s="3">
         <v>8537600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>14393500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>9143600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5160900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>3656200</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4132100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5875400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>10660100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>7868300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4810900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>3364900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>6012600</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>12134800</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>9365500</v>
+        <v>8190300</v>
       </c>
       <c r="E43" s="3">
+        <v>9391000</v>
+      </c>
+      <c r="F43" s="3">
         <v>11253600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8295200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4358400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>5092600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2734100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7857800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7273800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7230400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9334900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>20488500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>32414100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>24880100</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2650400</v>
+      </c>
+      <c r="E44" s="3">
         <v>2509100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4495000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3216200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1996300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1778700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1867400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2310300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2135300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2072600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2434900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5710700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>10333300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>7845700</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>31329700</v>
+        <v>12710400</v>
       </c>
       <c r="E45" s="3">
+        <v>27589300</v>
+      </c>
+      <c r="F45" s="3">
         <v>65046500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>90176300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>15765100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>17421200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>57505200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7029300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8048500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>9658500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>14969500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>16431000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>19849600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>19187100</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>59679500</v>
+        <v>36258400</v>
       </c>
       <c r="E46" s="3">
+        <v>55964400</v>
+      </c>
+      <c r="F46" s="3">
         <v>102877000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>117645900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>33301500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>31692300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>70429400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>28056000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>33082700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>29498100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>35009500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>29278200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>27423600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>34177800</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>10547100</v>
+        <v>10097300</v>
       </c>
       <c r="E47" s="3">
+        <v>10542700</v>
+      </c>
+      <c r="F47" s="3">
         <v>8699400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9495100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>9149800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>8512000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2097500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4630200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4974700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4795900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5536400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>6894900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>13053000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>16227900</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>24425800</v>
+        <v>38769000</v>
       </c>
       <c r="E48" s="3">
+        <v>31283300</v>
+      </c>
+      <c r="F48" s="3">
         <v>21058000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>19174300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>17105800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>17579400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>12737600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>28195200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>26602000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>31135900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>33973100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>89657600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>120179000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>82126800</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10589100</v>
+      </c>
+      <c r="E49" s="3">
         <v>10791400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6038300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6656400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5976800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5349600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2497100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>14414000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>13826200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>13975100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>13959300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>45685300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>53012500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>39782800</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2438,9 +2551,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2483,54 +2599,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>11430300</v>
+        <v>5838100</v>
       </c>
       <c r="E52" s="3">
+        <v>8312100</v>
+      </c>
+      <c r="F52" s="3">
         <v>8596800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7999500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>9251400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7805000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2917300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3771600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4410500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4530400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5684700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7292000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>12964100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>10999800</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2573,54 +2695,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>117711900</v>
+        <v>101915300</v>
       </c>
       <c r="E54" s="3">
+        <v>117731800</v>
+      </c>
+      <c r="F54" s="3">
         <v>148068800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>161843500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>75403100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>71831400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>91719700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>82923900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>82896200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>83935400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>94163000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>97348000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>97097200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>108732000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2638,8 +2766,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2657,278 +2786,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5672400</v>
+      </c>
+      <c r="E57" s="3">
         <v>5652700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7976900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5035800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2919900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3352000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2781100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6096300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5892600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6477100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6882600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7703500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>16086800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>18513300</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4035600</v>
+      </c>
+      <c r="E58" s="3">
         <v>3276200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11984600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>12505400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1525400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1895400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>877000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3346500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>958100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1298200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2391300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3765600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>12557800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>15247800</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>27587000</v>
+        <v>17867300</v>
       </c>
       <c r="E59" s="3">
+        <v>26287200</v>
+      </c>
+      <c r="F59" s="3">
         <v>63773600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>91554600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>14730300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>15889400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>48174900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12484400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>24360400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>18807000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>21511700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>34417100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>42894500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>39444700</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>37878900</v>
+        <v>28548500</v>
       </c>
       <c r="E60" s="3">
+        <v>36579000</v>
+      </c>
+      <c r="F60" s="3">
         <v>85160800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>110323000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>20184700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>22000900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>52489100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>24368400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>31211100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>26582300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>30785500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>26150100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>26651800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>36602900</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15293500</v>
+      </c>
+      <c r="E61" s="3">
         <v>15545500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>10461700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>7731100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4833000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4403500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2287600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>17307900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>16589600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>16969300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>15528000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>18527900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>16927900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>18109500</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>20235400</v>
+        <v>18831100</v>
       </c>
       <c r="E62" s="3">
+        <v>21535300</v>
+      </c>
+      <c r="F62" s="3">
         <v>18290100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>20045500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>21722300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>19529800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>14980500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>19478900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>26426300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>30974000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>35007300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>73540000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>104377000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>67904900</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2971,9 +3119,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3016,9 +3167,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3061,54 +3215,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>81081000</v>
+        <v>67105300</v>
       </c>
       <c r="E66" s="3">
+        <v>80588000</v>
+      </c>
+      <c r="F66" s="3">
         <v>116777800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>142514500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>53744300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>52229800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>75396200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>68525500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>79908100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>77749200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>86103300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>88091800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>83733500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>92266200</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3126,8 +3286,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3170,9 +3331,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3215,9 +3379,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3255,14 +3422,17 @@
         <v>0</v>
       </c>
       <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
         <v>109800</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>117400</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3305,54 +3475,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>15931200</v>
+        <v>19473000</v>
       </c>
       <c r="E72" s="3">
+        <v>16460700</v>
+      </c>
+      <c r="F72" s="3">
         <v>16814100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>12174500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>10156600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9996600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1304100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2842200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-707400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3821500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5463300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>8908100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>24317400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>15423900</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3395,9 +3571,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3440,9 +3619,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3485,54 +3667,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>34894400</v>
+        <v>32662800</v>
       </c>
       <c r="E76" s="3">
+        <v>35407300</v>
+      </c>
+      <c r="F76" s="3">
         <v>29471000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>17347900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>20692400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>19037100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>11078500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9244700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2988100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6186100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8059600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9256200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13254000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>16348800</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3575,104 +3763,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>1602700</v>
+        <v>5316300</v>
       </c>
       <c r="E81" s="3">
+        <v>1674600</v>
+      </c>
+      <c r="F81" s="3">
         <v>2903700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>820000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1285600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>9553400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>451100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2331900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-6195400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-179900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1858900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3297900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1434000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2119900</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3690,53 +3887,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1763000</v>
+        <v>1608900</v>
       </c>
       <c r="E83" s="3">
+        <v>1784000</v>
+      </c>
+      <c r="F83" s="3">
         <v>1532500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1415900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1603700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>813600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>922800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>-146500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7237000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5954400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3363300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>8745400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5880900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4041400</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3779,9 +3980,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3824,9 +4028,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3869,9 +4076,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3914,9 +4124,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3959,54 +4172,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>4681100</v>
+        <v>6853700</v>
       </c>
       <c r="E89" s="3">
+        <v>4667800</v>
+      </c>
+      <c r="F89" s="3">
         <v>2571300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>8272500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>5107000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-1709100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>7611600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2106100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2551900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3400400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6946900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>6670000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4825700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>6467700</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4024,53 +4243,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9708000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5688100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3530000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4195400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4107600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1987400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1426600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1083100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2504200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3357000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3654500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4696300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5578900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7457200</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4113,9 +4336,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4158,54 +4384,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-3106000</v>
+        <v>-10054900</v>
       </c>
       <c r="E94" s="3">
+        <v>-3092700</v>
+      </c>
+      <c r="F94" s="3">
         <v>-10571800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-8800200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-5326000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-818100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5042400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>3231300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4958500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2016500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5311600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2796700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1410900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9115800</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4223,53 +4455,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>770300</v>
+      </c>
+      <c r="E96" s="3">
         <v>739500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>650800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>653900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>638500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>628400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1173600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>190900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-441600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1132100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1157500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1927100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1708500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2700900</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4312,9 +4548,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4357,9 +4596,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4402,142 +4644,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1155400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1721000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>9207000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1657000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2171300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>251400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1133500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1844400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>4646000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2161500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2400000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2385200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2704400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2044800</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>154300</v>
+      </c>
+      <c r="E101" s="3">
         <v>67400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>36300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>66000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-41600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>16800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>14900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-22800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-26000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>14800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>8700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-21500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>17600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-14100</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1891500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-78500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1242900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1195300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1910700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2259000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1450700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-742100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2213400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-762800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-756000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1466500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>728000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-617400</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/RWEOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RWEOY_YR_FIN.xlsx
@@ -656,221 +656,233 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>25079200</v>
+        <v>21556900</v>
       </c>
       <c r="E8" s="3">
+        <v>25665200</v>
+      </c>
+      <c r="F8" s="3">
         <v>31525400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>41054800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>27943800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>16858700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>14837800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>15400700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>16658300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>47295200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>48507200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>50344400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>59509800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>55746600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>57696300</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>14600200</v>
+      </c>
+      <c r="E9" s="3">
         <v>16498600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>19512500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>33943600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>20807500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>12615300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10754100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>11979600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12642900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>35950400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>35441900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>36444000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>42205500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>37643800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>39455300</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>8580600</v>
+        <v>6956700</v>
       </c>
       <c r="E10" s="3">
+        <v>9166600</v>
+      </c>
+      <c r="F10" s="3">
         <v>12012800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7111300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7136400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4243400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4083700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3421100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4015400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>11344800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>13065200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>13900400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>17304200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>18102700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>18241000</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -889,37 +901,38 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E12" s="3">
+        <v>51800</v>
+      </c>
+      <c r="F12" s="3">
+        <v>19900</v>
+      </c>
+      <c r="G12" s="3">
+        <v>23500</v>
+      </c>
+      <c r="H12" s="3">
+        <v>27300</v>
+      </c>
+      <c r="I12" s="3">
         <v>26900</v>
       </c>
-      <c r="E12" s="3">
-        <v>19900</v>
-      </c>
-      <c r="F12" s="3">
-        <v>23500</v>
-      </c>
-      <c r="G12" s="3">
-        <v>27300</v>
-      </c>
-      <c r="H12" s="3">
-        <v>26900</v>
-      </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>32500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>166000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>343400</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -936,9 +949,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,105 +1000,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>974200</v>
+        <v>511900</v>
       </c>
       <c r="E14" s="3">
+        <v>668800</v>
+      </c>
+      <c r="F14" s="3">
         <v>1760800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-1961100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>562900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1958400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1325300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>26300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-1678700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4495200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2880900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>593500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>5705900</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2338900</v>
+      </c>
+      <c r="E15" s="3">
         <v>1941200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2101200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1742000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1616100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1741900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1344400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1031600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>563200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2459700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2551900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2478500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2997700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>5568000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>3995600</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1098,104 +1123,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>18048500</v>
+        <v>21048500</v>
       </c>
       <c r="E17" s="3">
+        <v>21664800</v>
+      </c>
+      <c r="F17" s="3">
         <v>25366400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>43172000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>26083200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13382300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>16362900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15147700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>16278800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>51764300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>48012000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>46471700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>59888900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>51524700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>52849600</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>7030700</v>
+        <v>508400</v>
       </c>
       <c r="E18" s="3">
+        <v>4000400</v>
+      </c>
+      <c r="F18" s="3">
         <v>6158900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-2117100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1860600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3476500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-1525100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>253000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>379400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4469100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>495100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3872700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-379200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4221800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4846700</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1214,248 +1246,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-597400</v>
+        <v>-3934500</v>
       </c>
       <c r="E20" s="3">
-        <v>-787000</v>
+        <v>-3547000</v>
       </c>
       <c r="F20" s="3">
+        <v>-848900</v>
+      </c>
+      <c r="G20" s="3">
         <v>-1724900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-439000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-237300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-318700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-85900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-401100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-839800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-38100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-244400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>570600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-401900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-49300</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>9569300</v>
+        <v>6781700</v>
       </c>
       <c r="E21" s="3">
-        <v>9047200</v>
+        <v>9488600</v>
       </c>
       <c r="F21" s="3">
+        <v>9109100</v>
+      </c>
+      <c r="G21" s="3">
         <v>1349800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3915600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>5455700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>138000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1370500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1343700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1925400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>6391200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7042800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8901000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>9709900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>8841500</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>895500</v>
+        <v>675100</v>
       </c>
       <c r="E22" s="3">
-        <v>1726500</v>
+        <v>1120200</v>
       </c>
       <c r="F22" s="3">
+        <v>1788400</v>
+      </c>
+      <c r="G22" s="3">
         <v>1185200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>449200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>554100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1179400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>446500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>559600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>991700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1131000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1178200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2602900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1371400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1247800</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4155200</v>
+      </c>
+      <c r="E23" s="3">
         <v>6566900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4420200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>764100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1730900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1547400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-843900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>56100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2468800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-6300600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-673900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2450200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2411500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2448500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3549600</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>185500</v>
+      </c>
+      <c r="E24" s="3">
         <v>1091200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2583200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-2433500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>784700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>459900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-103200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>117900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>399900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-350500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>638000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>603300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>884000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>577500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1002400</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1501,105 +1549,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3969700</v>
+      </c>
+      <c r="E26" s="3">
         <v>5475700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1837100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3197600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>946200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1087500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-740700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-61800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2068900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5950100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1311900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1846900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3295500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1871000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2547200</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3676200</v>
+      </c>
+      <c r="E27" s="3">
         <v>5316300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1674600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2903700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>820000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1285600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>9536500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>383600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2281500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6195400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1792300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1461800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3671100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1434000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2119900</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1645,9 +1702,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1664,38 +1724,41 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>270300</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>11015600</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>1290400</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>710900</v>
       </c>
-      <c r="L29" s="3" t="s">
+      <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>1612400</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>397100</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>373200</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1741,9 +1804,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1789,105 +1855,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>597400</v>
+        <v>3934500</v>
       </c>
       <c r="E32" s="3">
-        <v>787000</v>
+        <v>3547000</v>
       </c>
       <c r="F32" s="3">
+        <v>848900</v>
+      </c>
+      <c r="G32" s="3">
         <v>1724900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>439000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>237300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>318700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>85900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>401100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>839800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>38100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>244400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-570600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>401900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>49300</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3676200</v>
+      </c>
+      <c r="E33" s="3">
         <v>5316300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1674600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2903700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>820000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1285600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>9553400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>451100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2331900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6195400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-179900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1858900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3297900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1434000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2119900</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1933,110 +2008,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3676200</v>
+      </c>
+      <c r="E35" s="3">
         <v>5316300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1674600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2903700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>820000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1285600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>9553400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>451100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2331900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6195400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-179900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1858900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3297900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1434000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2119900</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2055,8 +2139,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2075,440 +2160,468 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9080700</v>
+      </c>
+      <c r="E41" s="3">
         <v>5269700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7645600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7468200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6624600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5839800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3582100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4033700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4722600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4965000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2668300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3459300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9450000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5662400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4307900</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6592700</v>
+      </c>
+      <c r="E42" s="3">
         <v>7092900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>8537600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>14393500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>9143600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>5160900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3656200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4132100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>5875400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>10660100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>7868300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4810900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>3364900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>6012600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>12134800</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>6982500</v>
+      </c>
+      <c r="E43" s="3">
         <v>8190300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9391000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>11253600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8295200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4358400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5092600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2734100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7857800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7273800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7230400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9334900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>20488500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>32414100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>24880100</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1789400</v>
+      </c>
+      <c r="E44" s="3">
         <v>2650400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2509100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>4495000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3216200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1996300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1778700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1867400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2310300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2135300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2072600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2434900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5710700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>10333300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>7845700</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>15447900</v>
+      </c>
+      <c r="E45" s="3">
         <v>12710400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>27589300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>65046500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>90176300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>15765100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>17421200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>57505200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7029300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8048500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>9658500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14969500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>16431000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>19849600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>19187100</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>40311100</v>
+      </c>
+      <c r="E46" s="3">
         <v>36258400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>55964400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>102877000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>117645900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>33301500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>31692300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>70429400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>28056000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>33082700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>29498100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>35009500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>29278200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>27423600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>34177800</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>10097300</v>
+        <v>5996200</v>
       </c>
       <c r="E47" s="3">
+        <v>4738600</v>
+      </c>
+      <c r="F47" s="3">
         <v>10542700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>8699400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>9495100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>9149800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8512000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2097500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4630200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4974700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4795900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>5536400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6894900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>13053000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>16227900</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>48164800</v>
+      </c>
+      <c r="E48" s="3">
         <v>38769000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>31283300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>21058000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>19174300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>17105800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>17579400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>12737600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>28195200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>26602000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>31135900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>33973100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>89657600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>120179000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>82126800</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>10589100</v>
+        <v>10169100</v>
       </c>
       <c r="E49" s="3">
+        <v>10591200</v>
+      </c>
+      <c r="F49" s="3">
         <v>10791400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6038300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>6656400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5976800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>5349600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2497100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>14414000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>13826200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>13975100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>13959300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>45685300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>53012500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>39782800</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2554,9 +2667,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2602,57 +2718,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>5838100</v>
+        <v>14359500</v>
       </c>
       <c r="E52" s="3">
+        <v>11196800</v>
+      </c>
+      <c r="F52" s="3">
         <v>8312100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8596800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7999500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9251400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7805000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2917300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3771600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4410500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4530400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5684700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7292000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>12964100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>10999800</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2698,57 +2820,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>101915300</v>
+        <v>119428200</v>
       </c>
       <c r="E54" s="3">
+        <v>101917400</v>
+      </c>
+      <c r="F54" s="3">
         <v>117731800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>148068800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>161843500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>75403100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>71831400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>91719700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>82923900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>82896200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>83935400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>94163000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>97348000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>97097200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>108732000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2767,8 +2895,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2787,296 +2916,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7048300</v>
+      </c>
+      <c r="E57" s="3">
         <v>5672400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5652700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>7976900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5035800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2919900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3352000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2781100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6096300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5892600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6477100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6882600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7703500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>16086800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>18513300</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4905500</v>
+      </c>
+      <c r="E58" s="3">
         <v>4035600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3276200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>11984600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12505400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1525400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1895400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>877000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3346500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>958100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1298200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2391300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3765600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>12557800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>15247800</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>13947400</v>
+      </c>
+      <c r="E59" s="3">
         <v>17867300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>26287200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>63773600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>91554600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>14730300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15889400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>48174900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12484400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>24360400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>18807000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>21511700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>34417100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>42894500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>39444700</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>26921500</v>
+      </c>
+      <c r="E60" s="3">
         <v>28548500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>36579000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>85160800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>110323000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>20184700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>22000900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>52489100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>24368400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>31211100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26582300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>30785500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>26150100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>26651800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>36602900</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18209500</v>
+      </c>
+      <c r="E61" s="3">
         <v>15293500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>15545500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10461700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7731100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4833000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4403500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2287600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>17307900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>16589600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>16969300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>15528000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>18527900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>16927900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>18109500</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>21176500</v>
+      </c>
+      <c r="E62" s="3">
         <v>18831100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>21535300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>18290100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>20045500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>21722300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>19529800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>14980500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>19478900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>26426300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>30974000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>35007300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>73540000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>104377000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>67904900</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3122,9 +3270,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3170,9 +3321,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3218,57 +3372,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>67105300</v>
+        <v>70627000</v>
       </c>
       <c r="E66" s="3">
+        <v>67107400</v>
+      </c>
+      <c r="F66" s="3">
         <v>80588000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>116777800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>142514500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>53744300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>52229800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>75396200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>68525500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>79908100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>77749200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>86103300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>88091800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>83733500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>92266200</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3287,8 +3447,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3334,9 +3495,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3382,9 +3546,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3425,14 +3592,17 @@
         <v>0</v>
       </c>
       <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
         <v>109800</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>117400</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3478,57 +3648,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>27207900</v>
+      </c>
+      <c r="E72" s="3">
         <v>19473000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>16460700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>16814100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>12174500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>10156600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>9996600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1304100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2842200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-707400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3821500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5463300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>8908100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>24317400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>15423900</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3574,9 +3750,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3622,9 +3801,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3670,57 +3852,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>40367500</v>
+      </c>
+      <c r="E76" s="3">
         <v>32662800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>35407300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>29471000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>17347900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20692400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19037100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>11078500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9244700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2988100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6186100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8059600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>9256200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13254000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>16348800</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3766,110 +3954,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3676200</v>
+      </c>
+      <c r="E81" s="3">
         <v>5316300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1674600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2903700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>820000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1285600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>9553400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>451100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2331900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6195400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-179900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1858900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3297900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1434000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2119900</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3888,56 +4085,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2092300</v>
+      </c>
+      <c r="E83" s="3">
         <v>1608900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1784000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1532500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1415900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1603700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>813600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>922800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>-146500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7237000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>5954400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3363300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>8745400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5880900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4041400</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3983,9 +4184,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4031,9 +4235,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4079,9 +4286,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4127,9 +4337,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4175,57 +4388,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5816600</v>
+      </c>
+      <c r="E89" s="3">
         <v>6853700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4667800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2571300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>8272500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>5107000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1709100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>7611600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2106100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2551900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3400400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>6946900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6670000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4825700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>6467700</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4244,56 +4463,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11757700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-9708000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-5688100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3530000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4195400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4107600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1987400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1426600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1083100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2504200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3357000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3654500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4696300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5578900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7457200</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4339,9 +4562,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4387,57 +4613,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-10675100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10054900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3092700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10571800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-8800200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5326000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-818100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5042400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>3231300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4958500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2016500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5311600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2796700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1410900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-9115800</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4456,56 +4688,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>949900</v>
+      </c>
+      <c r="E96" s="3">
         <v>770300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>739500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>650800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>653900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>638500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>628400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1173600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>190900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-441600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1132100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1157500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1927100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1708500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2700900</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4551,9 +4787,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4599,9 +4838,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4647,151 +4889,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>8349200</v>
+      </c>
+      <c r="E100" s="3">
         <v>1155400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1721000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>9207000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1657000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2171300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>251400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1133500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1844400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>4646000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2161500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2400000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2385200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2704400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2044800</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-386300</v>
+      </c>
+      <c r="E101" s="3">
         <v>154300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>67400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>36300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>66000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-41600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>16800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>14900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-22800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-26000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>14800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>8700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-21500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>17600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-14100</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3104400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1891500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-78500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1242900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1195300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1910700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2259000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1450700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-742100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2213400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-762800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-756000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1466500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>728000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-617400</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/RWEOY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/RWEOY_YR_FIN.xlsx
@@ -2473,10 +2473,10 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>5996200</v>
+        <v>14348900</v>
       </c>
       <c r="E47" s="3">
-        <v>4738600</v>
+        <v>10096300</v>
       </c>
       <c r="F47" s="3">
         <v>10542700</v>
@@ -2728,10 +2728,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>14359500</v>
+        <v>6006800</v>
       </c>
       <c r="E52" s="3">
-        <v>11196800</v>
+        <v>5839100</v>
       </c>
       <c r="F52" s="3">
         <v>8312100</v>
